--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -734,55 +734,55 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -893,10 +893,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1370,16 +1370,16 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1553,31 +1553,31 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1688,10 +1688,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,43 +1700,43 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1847,10 +1847,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,43 +1859,43 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,43 +2018,43 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2189,31 +2189,31 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,19 +2633,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -2654,10 +2654,10 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -2666,31 +2666,31 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -893,10 +893,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.23</v>
+        <v>1.93</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.15</v>
+        <v>1.93</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1211,10 +1211,10 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.93</v>
+        <v>2.23</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.93</v>
+        <v>1.15</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>6.16</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1541,43 +1541,43 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.94</v>
+        <v>2.63</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.8</v>
+        <v>2.04</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.85</v>
+        <v>1.49</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.84</v>
+        <v>2.33</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1688,10 +1688,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.74</v>
+        <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,43 +1700,43 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="V8" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="W8" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.6</v>
+        <v>6.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AF8" t="n">
         <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.9</v>
+        <v>1.05</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,43 +1859,43 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF9" t="n">
         <v>1.85</v>
       </c>
-      <c r="V9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AG9" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.05</v>
+        <v>2.25</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2006,10 +2006,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.94</v>
+        <v>1.74</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,43 +2018,43 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="V10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.68</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.64</v>
       </c>
       <c r="AE10" t="n">
         <v>1.26</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.35</v>
+        <v>2.9</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,19 +2474,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -2495,10 +2495,10 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -2507,31 +2507,31 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,19 +2633,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -2654,10 +2654,10 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -2666,31 +2666,31 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -893,10 +893,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.93</v>
+        <v>2.23</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.93</v>
+        <v>1.15</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1211,10 +1211,10 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.23</v>
+        <v>1.93</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.15</v>
+        <v>1.93</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1688,10 +1688,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>7</v>
+        <v>1.74</v>
       </c>
       <c r="R8" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,43 +1700,43 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="V8" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="W8" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.25</v>
+        <v>5.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AF8" t="n">
         <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.05</v>
+        <v>2.9</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2006,10 +2006,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.74</v>
+        <v>7</v>
       </c>
       <c r="R10" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,43 +2018,43 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="V10" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="W10" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.6</v>
+        <v>6.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AF10" t="n">
         <v>1.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.9</v>
+        <v>1.05</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,19 +2315,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2336,10 +2336,10 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -2348,31 +2348,31 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,19 +2474,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -2495,10 +2495,10 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -2507,31 +2507,31 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -893,10 +893,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1529,10 +1529,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1541,43 +1541,43 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,44 +1700,44 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.08</v>
       </c>
-      <c r="Z8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC8" t="n">
+      <c r="AF8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.98</v>
       </c>
-      <c r="AD8" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.9</v>
+        <v>1.42</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>6.16</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1871,31 +1871,31 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2006,10 +2006,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,43 +2018,43 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.38</v>
+        <v>1.46</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="P11" t="n">
-        <v>2.65</v>
+        <v>6.16</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2189,31 +2189,31 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.42</v>
+        <v>2.25</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,19 +2315,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2336,10 +2336,10 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -2348,31 +2348,31 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,19 +2474,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -2495,10 +2495,10 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -2507,31 +2507,31 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="O2" t="n">
         <v>4.62</v>
       </c>
       <c r="P2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="Q2" t="n">
         <v>1.83</v>
@@ -752,7 +752,7 @@
         <v>1.38</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
@@ -764,10 +764,10 @@
         <v>3.34</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC2" t="n">
         <v>2.97</v>
@@ -782,7 +782,7 @@
         <v>2.14</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.98</v>
+        <v>3.03</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1052,10 +1052,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1064,10 +1064,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q6" t="n">
         <v>2.95</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.38</v>
+        <v>1.35</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="P8" t="n">
-        <v>2.65</v>
+        <v>6.94</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,19 +2474,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -2495,10 +2495,10 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -2507,31 +2507,31 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,19 +2633,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -2654,10 +2654,10 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -2666,31 +2666,31 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -1529,10 +1529,10 @@
         <v>1.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1541,43 +1541,43 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.35</v>
+        <v>2.38</v>
       </c>
       <c r="O8" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>6.94</v>
+        <v>2.65</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="O9" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="P9" t="n">
-        <v>5.33</v>
+        <v>6.94</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,43 +1859,43 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.38</v>
+        <v>1.46</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="P10" t="n">
-        <v>2.65</v>
+        <v>6.16</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.42</v>
+        <v>2.25</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="O11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P11" t="n">
-        <v>6.16</v>
+        <v>5.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,43 +2177,43 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.94</v>
+        <v>2.63</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.8</v>
+        <v>2.04</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>1.49</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.84</v>
+        <v>2.33</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,19 +2474,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -2495,10 +2495,10 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -2507,31 +2507,31 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,19 +2633,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -2654,10 +2654,10 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -2666,31 +2666,31 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1052,10 +1052,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1064,10 +1064,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1211,10 +1211,10 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>9.15</v>
+        <v>2.38</v>
       </c>
       <c r="O7" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.23</v>
+        <v>2.65</v>
       </c>
       <c r="Q7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1541,43 +1541,43 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.25</v>
+        <v>3.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.29</v>
+        <v>1.86</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.1</v>
+        <v>1.78</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.78</v>
+        <v>3.15</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.86</v>
+        <v>1.28</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.05</v>
+        <v>1.42</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.38</v>
+        <v>1.35</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="P8" t="n">
-        <v>2.65</v>
+        <v>6.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,43 +1700,43 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.25</v>
+        <v>5.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.86</v>
+        <v>1.38</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.78</v>
+        <v>2.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.15</v>
+        <v>1.98</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.34</v>
+        <v>1.13</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.42</v>
+        <v>2.9</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="O9" t="n">
+        <v>6</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>7</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.35</v>
-      </c>
-      <c r="O9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P9" t="n">
-        <v>6.94</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.26</v>
       </c>
       <c r="AF9" t="n">
         <v>1.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.9</v>
+        <v>1.05</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,19 +2474,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -2495,10 +2495,10 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -2507,31 +2507,31 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,19 +2633,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -2654,10 +2654,10 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -2666,31 +2666,31 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2795,55 +2795,55 @@
         <v>1.58</v>
       </c>
       <c r="O15" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
-        <v>5.48</v>
+        <v>5.25</v>
       </c>
       <c r="Q15" t="n">
         <v>2.1</v>
       </c>
       <c r="R15" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S15" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T15" t="n">
         <v>2.5</v>
       </c>
       <c r="U15" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="V15" t="n">
         <v>1.29</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="Z15" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
         <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="AD15" t="n">
         <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AF15" t="n">
         <v>2.05</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1052,10 +1052,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1064,10 +1064,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1211,10 +1211,10 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.38</v>
+        <v>9.15</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="P7" t="n">
-        <v>2.65</v>
+        <v>1.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1541,43 +1541,43 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.25</v>
+        <v>6.25</v>
       </c>
       <c r="AA7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.86</v>
       </c>
-      <c r="AB7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AE7" t="n">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.34</v>
+        <v>1.09</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.42</v>
+        <v>1.05</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="O8" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="P8" t="n">
-        <v>6.94</v>
+        <v>5.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.74</v>
+        <v>1.94</v>
       </c>
       <c r="R8" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,43 +1700,43 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="V8" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="W8" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AE8" t="n">
         <v>1.26</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>9.15</v>
+        <v>2.38</v>
       </c>
       <c r="O9" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>1.23</v>
+        <v>2.65</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,43 +1859,43 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.25</v>
+        <v>3.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.29</v>
+        <v>1.86</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.1</v>
+        <v>1.78</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.78</v>
+        <v>3.15</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.86</v>
+        <v>1.28</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.05</v>
+        <v>1.42</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="O10" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="P10" t="n">
-        <v>6.16</v>
+        <v>6.94</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,43 +2018,43 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.72</v>
+        <v>1.38</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.94</v>
+        <v>2.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.35</v>
+        <v>1.68</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="O11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P11" t="n">
-        <v>5.33</v>
+        <v>6.16</v>
       </c>
       <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1.94</v>
       </c>
-      <c r="R11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.63</v>
-      </c>
       <c r="AC11" t="n">
-        <v>2.04</v>
+        <v>2.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.64</v>
+        <v>1.35</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.33</v>
+        <v>1.84</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -893,10 +893,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.93</v>
+        <v>2.23</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.93</v>
+        <v>1.15</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1052,10 +1052,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1064,10 +1064,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>9.15</v>
+        <v>1.35</v>
       </c>
       <c r="O7" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="P7" t="n">
-        <v>1.23</v>
+        <v>6.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>7</v>
+        <v>1.74</v>
       </c>
       <c r="R7" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1541,43 +1541,43 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="V7" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="W7" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.25</v>
+        <v>5.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AF7" t="n">
         <v>1.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.05</v>
+        <v>2.9</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="O8" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>5.33</v>
+        <v>2.65</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,59 +1700,59 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.3</v>
+        <v>3.25</v>
       </c>
       <c r="AA8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.42</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2.35</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.38</v>
+        <v>9.15</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="P9" t="n">
-        <v>2.65</v>
+        <v>1.23</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,43 +1859,43 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.25</v>
+        <v>6.25</v>
       </c>
       <c r="AA9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.86</v>
       </c>
-      <c r="AB9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AE9" t="n">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.34</v>
+        <v>1.09</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.42</v>
+        <v>1.05</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.35</v>
       </c>
-      <c r="O10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P10" t="n">
-        <v>6.94</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AE10" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="O11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P11" t="n">
-        <v>6.16</v>
+        <v>5.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,43 +2177,43 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.94</v>
+        <v>2.63</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.8</v>
+        <v>2.04</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>1.49</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.84</v>
+        <v>2.33</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,19 +2315,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2336,10 +2336,10 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -2348,31 +2348,31 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,19 +2633,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -2654,10 +2654,10 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -2666,31 +2666,31 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -734,7 +734,7 @@
         <v>9.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="R2" t="n">
         <v>2.4</v>
@@ -758,16 +758,16 @@
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z2" t="n">
         <v>3.34</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC2" t="n">
         <v>2.97</v>
@@ -798,7 +798,7 @@
         <v>1.05</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.03</v>
+        <v>2.5</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -893,10 +893,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.23</v>
+        <v>1.93</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.15</v>
+        <v>1.93</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1052,10 +1052,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1064,10 +1064,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="O7" t="n">
+        <v>6</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>7</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.35</v>
-      </c>
-      <c r="O7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P7" t="n">
-        <v>6.94</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.26</v>
       </c>
       <c r="AF7" t="n">
         <v>1.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.9</v>
+        <v>1.05</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.38</v>
+        <v>1.46</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="P8" t="n">
-        <v>2.65</v>
+        <v>6.16</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.42</v>
+        <v>2.25</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>9.15</v>
+        <v>2.38</v>
       </c>
       <c r="O9" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>1.23</v>
+        <v>2.65</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,43 +1859,43 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.25</v>
+        <v>3.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.29</v>
+        <v>1.86</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.1</v>
+        <v>1.78</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.78</v>
+        <v>3.15</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.86</v>
+        <v>1.28</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.05</v>
+        <v>1.42</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="O10" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="P10" t="n">
-        <v>6.16</v>
+        <v>6.94</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,43 +2018,43 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.72</v>
+        <v>1.38</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.94</v>
+        <v>2.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.35</v>
+        <v>1.68</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,19 +2315,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2336,10 +2336,10 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -2348,31 +2348,31 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,19 +2474,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -2495,10 +2495,10 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -2507,31 +2507,31 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2795,10 +2795,10 @@
         <v>1.58</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="Q15" t="n">
         <v>2.1</v>
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -893,10 +893,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.93</v>
+        <v>2.23</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.93</v>
+        <v>1.15</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1052,10 +1052,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1064,10 +1064,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>9.15</v>
+        <v>2.38</v>
       </c>
       <c r="O7" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.23</v>
+        <v>2.65</v>
       </c>
       <c r="Q7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1541,43 +1541,43 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.25</v>
+        <v>3.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.29</v>
+        <v>1.86</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.1</v>
+        <v>1.78</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.78</v>
+        <v>3.15</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.86</v>
+        <v>1.28</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.05</v>
+        <v>1.42</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.46</v>
+        <v>9.15</v>
       </c>
       <c r="O8" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="P8" t="n">
-        <v>6.16</v>
+        <v>1.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,43 +1700,43 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.6</v>
+        <v>6.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.72</v>
+        <v>1.29</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.94</v>
+        <v>3.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.8</v>
+        <v>1.78</v>
       </c>
       <c r="AD8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.35</v>
       </c>
-      <c r="AE8" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.25</v>
+        <v>1.05</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.38</v>
+        <v>1.5</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.65</v>
+        <v>5.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,43 +1859,43 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.25</v>
+        <v>5.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.86</v>
+        <v>1.42</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.78</v>
+        <v>2.63</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.15</v>
+        <v>2.04</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.28</v>
+        <v>1.64</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.98</v>
+        <v>2.33</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.42</v>
+        <v>2.35</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="O11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P11" t="n">
-        <v>5.33</v>
+        <v>6.16</v>
       </c>
       <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1.94</v>
       </c>
-      <c r="R11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.63</v>
-      </c>
       <c r="AC11" t="n">
-        <v>2.04</v>
+        <v>2.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.64</v>
+        <v>1.35</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.33</v>
+        <v>1.84</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -740,10 +740,10 @@
         <v>2.4</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T2" t="n">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="U2" t="n">
         <v>2.7</v>
@@ -758,19 +758,19 @@
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z2" t="n">
         <v>3.34</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AD2" t="n">
         <v>1.3</v>
@@ -779,10 +779,10 @@
         <v>1.08</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -893,10 +893,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1211,10 +1211,10 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.93</v>
+        <v>2.23</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.93</v>
+        <v>1.15</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.38</v>
+        <v>1.35</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="P7" t="n">
-        <v>2.65</v>
+        <v>6.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1541,43 +1541,43 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.25</v>
+        <v>5.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.86</v>
+        <v>1.38</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.78</v>
+        <v>2.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.15</v>
+        <v>1.98</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.34</v>
+        <v>1.13</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.42</v>
+        <v>2.9</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>9.15</v>
+        <v>2.38</v>
       </c>
       <c r="O8" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.23</v>
+        <v>2.65</v>
       </c>
       <c r="Q8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,43 +1700,43 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.25</v>
+        <v>3.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.29</v>
+        <v>1.86</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.1</v>
+        <v>1.78</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.78</v>
+        <v>3.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.86</v>
+        <v>1.28</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.05</v>
+        <v>1.42</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="O10" t="n">
+        <v>6</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.35</v>
-      </c>
-      <c r="O10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P10" t="n">
-        <v>6.94</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.26</v>
       </c>
       <c r="AF10" t="n">
         <v>1.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.9</v>
+        <v>1.05</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,19 +2315,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2336,10 +2336,10 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -2348,31 +2348,31 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,19 +2474,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -2495,10 +2495,10 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -2507,31 +2507,31 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -893,10 +893,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1211,10 +1211,10 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="O7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.35</v>
       </c>
-      <c r="O7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P7" t="n">
-        <v>6.94</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AE7" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.38</v>
+        <v>9.15</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="P8" t="n">
-        <v>2.65</v>
+        <v>1.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,43 +1700,43 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.25</v>
+        <v>6.25</v>
       </c>
       <c r="AA8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.86</v>
       </c>
-      <c r="AB8" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.34</v>
+        <v>1.09</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.42</v>
+        <v>1.05</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>9.15</v>
+        <v>2.38</v>
       </c>
       <c r="O10" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>1.23</v>
+        <v>2.65</v>
       </c>
       <c r="Q10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,43 +2018,43 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.25</v>
+        <v>3.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.29</v>
+        <v>1.86</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.1</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.78</v>
+        <v>3.15</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.86</v>
+        <v>1.28</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.05</v>
+        <v>1.42</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="O11" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="P11" t="n">
-        <v>6.16</v>
+        <v>6.94</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,43 +2177,43 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.72</v>
+        <v>1.38</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.94</v>
+        <v>2.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.35</v>
+        <v>1.68</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,19 +2315,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2336,10 +2336,10 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -2348,31 +2348,31 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,19 +2474,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -2495,10 +2495,10 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -2507,31 +2507,31 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -734,16 +734,16 @@
         <v>9.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="S2" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="U2" t="n">
         <v>2.7</v>
@@ -752,7 +752,7 @@
         <v>1.38</v>
       </c>
       <c r="W2" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
@@ -761,13 +761,13 @@
         <v>1.24</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC2" t="n">
         <v>3.1</v>
@@ -782,7 +782,7 @@
         <v>2.02</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>1.05</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.5</v>
+        <v>3.03</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -893,10 +893,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,19 +1043,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1064,10 +1064,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.93</v>
+        <v>2.23</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.93</v>
+        <v>1.15</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.46</v>
+        <v>9.15</v>
       </c>
       <c r="O7" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="P7" t="n">
-        <v>6.16</v>
+        <v>1.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1541,43 +1541,43 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.6</v>
+        <v>6.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>1.29</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.94</v>
+        <v>3.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.8</v>
+        <v>1.78</v>
       </c>
       <c r="AD7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.35</v>
       </c>
-      <c r="AE7" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AF7" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.16</v>
+        <v>3.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.25</v>
+        <v>1.05</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>9.15</v>
+        <v>1.35</v>
       </c>
       <c r="O8" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="P8" t="n">
-        <v>1.23</v>
+        <v>6.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>7</v>
+        <v>1.74</v>
       </c>
       <c r="R8" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,43 +1700,43 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="V8" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="W8" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.25</v>
+        <v>5.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AF8" t="n">
         <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.05</v>
+        <v>2.9</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="O9" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>5.33</v>
+        <v>2.65</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,59 +1859,59 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.3</v>
+        <v>3.25</v>
       </c>
       <c r="AA9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AK9" t="n">
         <v>1.42</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.35</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.38</v>
+        <v>1.5</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.65</v>
+        <v>5.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,43 +2018,43 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.25</v>
+        <v>5.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.86</v>
+        <v>1.42</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>2.63</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.15</v>
+        <v>2.04</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.28</v>
+        <v>1.64</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.98</v>
+        <v>2.33</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.42</v>
+        <v>2.35</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.35</v>
       </c>
-      <c r="O11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P11" t="n">
-        <v>6.94</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AE11" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,19 +2474,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -2495,10 +2495,10 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -2507,31 +2507,31 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,19 +2633,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -2654,10 +2654,10 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -2666,31 +2666,31 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2795,10 +2795,10 @@
         <v>1.58</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P15" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="Q15" t="n">
         <v>2.1</v>
@@ -2807,16 +2807,16 @@
         <v>2.1</v>
       </c>
       <c r="S15" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T15" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U15" t="n">
-        <v>3.14</v>
+        <v>3.33</v>
       </c>
       <c r="V15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W15" t="n">
         <v>1.02</v>
@@ -2843,10 +2843,10 @@
         <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
         <v>1.73</v>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB16" t="n">
         <v>2.04</v>
       </c>
-      <c r="O16" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="P16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="O17" t="n">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="P17" t="n">
-        <v>4.31</v>
+        <v>4.39</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="O18" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="P18" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>9.15</v>
+        <v>1.35</v>
       </c>
       <c r="O7" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="P7" t="n">
-        <v>1.23</v>
+        <v>6.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>7</v>
+        <v>1.74</v>
       </c>
       <c r="R7" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1541,43 +1541,43 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="V7" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="W7" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.25</v>
+        <v>5.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AF7" t="n">
         <v>1.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>3.5</v>
+        <v>1.13</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.05</v>
+        <v>2.9</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.35</v>
       </c>
-      <c r="O8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P8" t="n">
-        <v>6.94</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.38</v>
+        <v>1.5</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.65</v>
+        <v>5.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,43 +1859,43 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.25</v>
+        <v>5.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.86</v>
+        <v>1.42</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.78</v>
+        <v>2.63</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.15</v>
+        <v>2.04</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.28</v>
+        <v>1.64</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.98</v>
+        <v>2.33</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.42</v>
+        <v>2.35</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.5</v>
+        <v>9.15</v>
       </c>
       <c r="O10" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>5.33</v>
+        <v>1.23</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.94</v>
+        <v>7</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,43 +2018,43 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="V10" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="W10" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.3</v>
+        <v>6.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.04</v>
+        <v>1.78</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.64</v>
+        <v>1.86</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.17</v>
+        <v>3.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.35</v>
+        <v>1.05</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.46</v>
+        <v>2.38</v>
       </c>
       <c r="O11" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>6.16</v>
+        <v>2.65</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2189,31 +2189,31 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.25</v>
+        <v>1.42</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2792,10 +2792,10 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="O15" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="P15" t="n">
         <v>4.8</v>
@@ -2819,7 +2819,7 @@
         <v>1.3</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
         <v>1.06</v>
@@ -2837,7 +2837,7 @@
         <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="AD15" t="n">
         <v>1.22</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.93</v>
+        <v>2.23</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.93</v>
+        <v>1.15</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1052,10 +1052,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1064,10 +1064,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.46</v>
+        <v>9.15</v>
       </c>
       <c r="O8" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="P8" t="n">
-        <v>6.16</v>
+        <v>1.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,43 +1700,43 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.6</v>
+        <v>6.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.72</v>
+        <v>1.29</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.94</v>
+        <v>3.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.8</v>
+        <v>1.78</v>
       </c>
       <c r="AD8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.35</v>
       </c>
-      <c r="AE8" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.16</v>
+        <v>3.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.25</v>
+        <v>1.05</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>9.15</v>
+        <v>2.38</v>
       </c>
       <c r="O10" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>1.23</v>
+        <v>2.65</v>
       </c>
       <c r="Q10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,43 +2018,43 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.25</v>
+        <v>3.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.29</v>
+        <v>1.86</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.1</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.78</v>
+        <v>3.15</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.86</v>
+        <v>1.28</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>3.5</v>
+        <v>1.34</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.05</v>
+        <v>1.42</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.38</v>
+        <v>1.46</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="P11" t="n">
-        <v>2.65</v>
+        <v>6.16</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2189,31 +2189,31 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.42</v>
+        <v>2.25</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,19 +2474,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -2495,10 +2495,10 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -2507,31 +2507,31 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,19 +2633,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -2654,10 +2654,10 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -2666,31 +2666,31 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.23</v>
+        <v>1.93</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.15</v>
+        <v>1.93</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.93</v>
+        <v>2.23</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.93</v>
+        <v>1.15</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.38</v>
+        <v>1.46</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="P10" t="n">
-        <v>2.65</v>
+        <v>6.16</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.42</v>
+        <v>2.25</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.46</v>
+        <v>2.38</v>
       </c>
       <c r="O11" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>6.16</v>
+        <v>2.65</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2189,31 +2189,31 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.25</v>
+        <v>1.42</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,19 +2315,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2336,10 +2336,10 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -2348,31 +2348,31 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,19 +2474,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -2495,10 +2495,10 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -2507,31 +2507,31 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2963,13 +2963,13 @@
         <v>2.48</v>
       </c>
       <c r="R16" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="S16" t="n">
         <v>1.28</v>
       </c>
       <c r="T16" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="U16" t="n">
         <v>2.54</v>
@@ -2984,16 +2984,16 @@
         <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="AA16" t="n">
         <v>1.69</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AC16" t="n">
         <v>2.66</v>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3113,16 +3113,16 @@
         <v>1.62</v>
       </c>
       <c r="O17" t="n">
-        <v>3.94</v>
+        <v>3.7</v>
       </c>
       <c r="P17" t="n">
-        <v>4.39</v>
+        <v>4.15</v>
       </c>
       <c r="Q17" t="n">
         <v>2.14</v>
       </c>
       <c r="R17" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="S17" t="n">
         <v>1.26</v>
@@ -3137,7 +3137,7 @@
         <v>1.54</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
@@ -3149,16 +3149,16 @@
         <v>4.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE17" t="n">
         <v>1.15</v>
@@ -3167,7 +3167,7 @@
         <v>1.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3269,13 +3269,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="O18" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P18" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q18" t="n">
         <v>2.5</v>
@@ -3299,34 +3299,34 @@
         <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.49</v>
+        <v>3.42</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF18" t="n">
         <v>1.71</v>
       </c>
       <c r="AG18" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK18" t="n">
         <v>1.74</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -758,22 +758,22 @@
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.45</v>
+        <v>3.34</v>
       </c>
       <c r="AA2" t="n">
         <v>1.83</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AC2" t="n">
         <v>3.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE2" t="n">
         <v>1.08</v>
@@ -782,7 +782,7 @@
         <v>2.02</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1052,10 +1052,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1064,10 +1064,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1211,10 +1211,10 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="O7" t="n">
+        <v>6</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>7</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.35</v>
-      </c>
-      <c r="O7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P7" t="n">
-        <v>6.94</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.26</v>
       </c>
       <c r="AF7" t="n">
         <v>1.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.13</v>
+        <v>3.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.9</v>
+        <v>1.05</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>9.15</v>
+        <v>1.46</v>
       </c>
       <c r="O8" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="P8" t="n">
-        <v>1.23</v>
+        <v>6.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,43 +1700,43 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.85</v>
       </c>
-      <c r="V8" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AG8" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>3.5</v>
+        <v>1.16</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.05</v>
+        <v>2.25</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="O9" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="P9" t="n">
-        <v>5.33</v>
+        <v>6.94</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.94</v>
+        <v>1.74</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,43 +1859,43 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="V9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.68</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.64</v>
       </c>
       <c r="AE9" t="n">
         <v>1.26</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.35</v>
+        <v>2.9</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="O10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P10" t="n">
-        <v>6.16</v>
+        <v>5.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,43 +2018,43 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.94</v>
+        <v>2.63</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.8</v>
+        <v>2.04</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>1.49</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.84</v>
+        <v>2.33</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,19 +2315,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2336,10 +2336,10 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -2348,31 +2348,31 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,19 +2474,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -2495,10 +2495,10 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -2507,31 +2507,31 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2966,7 +2966,7 @@
         <v>2.33</v>
       </c>
       <c r="S16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T16" t="n">
         <v>3.2</v>
@@ -2990,25 +2990,25 @@
         <v>3.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB16" t="n">
         <v>2.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="AD16" t="n">
         <v>1.37</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK16" t="n">
         <v>1.62</v>
@@ -3131,10 +3131,10 @@
         <v>3.32</v>
       </c>
       <c r="U17" t="n">
-        <v>2.41</v>
+        <v>2.27</v>
       </c>
       <c r="V17" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W17" t="n">
         <v>1.13</v>
@@ -3149,10 +3149,10 @@
         <v>4.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AC17" t="n">
         <v>2.58</v>
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="O18" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>3.3</v>
+        <v>4.11</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="R18" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="S18" t="n">
         <v>1.33</v>
       </c>
       <c r="T18" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W18" t="n">
         <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF18" t="n">
         <v>1.71</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,19 +1043,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1064,10 +1064,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.23</v>
+        <v>1.93</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.15</v>
+        <v>1.93</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1211,10 +1211,10 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1559,19 +1559,19 @@
         <v>6.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AB7" t="n">
         <v>3.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AF7" t="n">
         <v>1.6</v>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>3.5</v>
+        <v>1.09</v>
       </c>
       <c r="AK7" t="n">
         <v>1.05</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="O8" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="P8" t="n">
-        <v>6.16</v>
+        <v>6.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,43 +1700,43 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.94</v>
+        <v>2.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.35</v>
+        <v>1.68</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="O9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.35</v>
       </c>
-      <c r="O9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P9" t="n">
-        <v>6.94</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AE9" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="O10" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>5.33</v>
+        <v>2.65</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,59 +2018,59 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.3</v>
+        <v>3.25</v>
       </c>
       <c r="AA10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AK10" t="n">
         <v>1.42</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.35</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.38</v>
+        <v>1.5</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.65</v>
+        <v>5.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,43 +2177,43 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.25</v>
+        <v>5.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.86</v>
+        <v>1.42</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>2.63</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.15</v>
+        <v>2.06</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.28</v>
+        <v>1.66</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.98</v>
+        <v>2.33</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.42</v>
+        <v>2.35</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,19 +2315,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2336,10 +2336,10 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -2348,31 +2348,31 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,19 +2474,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -2495,10 +2495,10 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -2507,31 +2507,31 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2819,7 +2819,7 @@
         <v>1.3</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
         <v>1.06</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,19 +1043,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1064,10 +1064,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.93</v>
+        <v>2.23</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.93</v>
+        <v>1.15</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.23</v>
+        <v>1.93</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.15</v>
+        <v>1.93</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>9.15</v>
+        <v>1.35</v>
       </c>
       <c r="O7" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="P7" t="n">
-        <v>1.23</v>
+        <v>6.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>7</v>
+        <v>1.74</v>
       </c>
       <c r="R7" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1541,43 +1541,43 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="V7" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="W7" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.25</v>
+        <v>5.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="AF7" t="n">
         <v>1.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.05</v>
+        <v>2.9</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.35</v>
       </c>
-      <c r="O8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="P8" t="n">
-        <v>6.94</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.46</v>
+        <v>9.15</v>
       </c>
       <c r="O9" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="P9" t="n">
-        <v>6.16</v>
+        <v>1.23</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,43 +1859,43 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.6</v>
+        <v>6.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.72</v>
+        <v>1.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.94</v>
+        <v>3.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.35</v>
+        <v>1.88</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.25</v>
+        <v>1.05</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,19 +1997,19 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.38</v>
+        <v>1.5</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.65</v>
+        <v>5.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2018,43 +2018,43 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.25</v>
+        <v>5.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.86</v>
+        <v>1.42</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>2.63</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.15</v>
+        <v>2.06</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.28</v>
+        <v>1.66</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.98</v>
+        <v>2.33</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.42</v>
+        <v>2.35</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,19 +2156,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="O11" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>5.33</v>
+        <v>2.65</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2177,59 +2177,59 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.3</v>
+        <v>3.25</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AK11" t="n">
         <v>1.42</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2.35</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,19 +1043,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1064,10 +1064,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.23</v>
+        <v>1.93</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.15</v>
+        <v>1.93</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.93</v>
+        <v>2.23</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.93</v>
+        <v>1.15</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.35</v>
+        <v>9.15</v>
       </c>
       <c r="O7" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="P7" t="n">
-        <v>6.94</v>
+        <v>1.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.74</v>
+        <v>7</v>
       </c>
       <c r="R7" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1541,43 +1541,43 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="V7" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="W7" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.6</v>
+        <v>6.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="AF7" t="n">
         <v>1.6</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.9</v>
+        <v>1.05</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="O8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P8" t="n">
-        <v>6.16</v>
+        <v>5.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1700,43 +1700,43 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.94</v>
+        <v>2.63</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.8</v>
+        <v>2.06</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.35</v>
+        <v>1.66</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.85</v>
+        <v>1.49</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.84</v>
+        <v>2.33</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>9.15</v>
+        <v>1.35</v>
       </c>
       <c r="O9" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="P9" t="n">
-        <v>1.23</v>
+        <v>6.94</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>1.74</v>
       </c>
       <c r="R9" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,43 +1859,43 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="V9" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="W9" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.25</v>
+        <v>5.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="AF9" t="n">
         <v>1.6</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.05</v>
+        <v>2.9</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="O10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P10" t="n">
-        <v>5.33</v>
+        <v>6.16</v>
       </c>
       <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB10" t="n">
         <v>1.94</v>
       </c>
-      <c r="R10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.63</v>
-      </c>
       <c r="AC10" t="n">
-        <v>2.06</v>
+        <v>2.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.66</v>
+        <v>1.35</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.33</v>
+        <v>1.84</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU18"/>
+  <dimension ref="A1:AU22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -737,7 +737,7 @@
         <v>1.83</v>
       </c>
       <c r="R2" t="n">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="S2" t="n">
         <v>1.3</v>
@@ -761,16 +761,16 @@
         <v>1.26</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AB2" t="n">
         <v>1.86</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AD2" t="n">
         <v>1.32</v>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AK2" t="n">
         <v>3.03</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -893,10 +893,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -905,10 +905,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -917,31 +917,31 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.69</v>
+        <v>2.26</v>
       </c>
       <c r="O4" t="n">
-        <v>3.65</v>
+        <v>2.88</v>
       </c>
       <c r="P4" t="n">
-        <v>4.43</v>
+        <v>3.11</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1076,31 +1076,31 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,19 +1202,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1235,31 +1235,31 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1314,27 +1314,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,25 +1361,25 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.47</v>
+        <v>1.89</v>
       </c>
       <c r="O6" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>2.6</v>
+        <v>4.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1394,31 +1394,31 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="AU6" s="3" t="n">
-        <v>46190.52083333334</v>
+        <v>46190.5</v>
       </c>
     </row>
     <row r="7">
@@ -1473,27 +1473,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>9.15</v>
+        <v>2.28</v>
       </c>
       <c r="O7" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="P7" t="n">
-        <v>1.23</v>
+        <v>3.17</v>
       </c>
       <c r="Q7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1541,43 +1541,43 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         <v>0</v>
       </c>
       <c r="AU7" s="3" t="n">
-        <v>46190.54166666666</v>
+        <v>46190.5</v>
       </c>
     </row>
     <row r="8">
@@ -1632,12 +1632,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,65 +1679,65 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="O8" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="P8" t="n">
-        <v>5.33</v>
+        <v>4.43</v>
       </c>
       <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.94</v>
       </c>
-      <c r="R8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.33</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.35</v>
+        <v>1.93</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1782,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="AU8" s="3" t="n">
-        <v>46190.54166666666</v>
+        <v>46190.5</v>
       </c>
     </row>
     <row r="9">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>6.94</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1859,43 +1859,43 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="AU9" s="3" t="n">
-        <v>46190.54166666666</v>
+        <v>46190.5</v>
       </c>
     </row>
     <row r="10">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,25 +1997,25 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.46</v>
+        <v>2.47</v>
       </c>
       <c r="O10" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>6.16</v>
+        <v>2.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -2030,31 +2030,31 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AA10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB10" t="n">
         <v>1.72</v>
       </c>
-      <c r="AB10" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AC10" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.25</v>
+        <v>1.42</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2100,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="AU10" s="3" t="n">
-        <v>46190.54166666666</v>
+        <v>46190.52083333334</v>
       </c>
     </row>
     <row r="11">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,19 +2315,19 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.53</v>
+        <v>9.15</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>5.23</v>
+        <v>1.23</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.95</v>
+        <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2336,43 +2336,43 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.28</v>
+        <v>1.85</v>
       </c>
       <c r="V12" t="n">
-        <v>1.49</v>
+        <v>1.83</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.95</v>
+        <v>6.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.58</v>
+        <v>1.29</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.04</v>
+        <v>3.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.5</v>
+        <v>1.78</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.38</v>
+        <v>1.86</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.12</v>
+        <v>1.35</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.18</v>
+        <v>1.05</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="AU12" s="3" t="n">
-        <v>46190.58333333334</v>
+        <v>46190.54166666666</v>
       </c>
     </row>
     <row r="13">
@@ -2427,12 +2427,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>6.16</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2507,31 +2507,31 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="AU13" s="3" t="n">
-        <v>46190.58333333334</v>
+        <v>46190.54166666666</v>
       </c>
     </row>
     <row r="14">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,19 +2633,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -2654,43 +2654,43 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="AU14" s="3" t="n">
-        <v>46190.58333333334</v>
+        <v>46190.54166666666</v>
       </c>
     </row>
     <row r="15">
@@ -2745,12 +2745,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.64</v>
+        <v>1.35</v>
       </c>
       <c r="O15" t="n">
-        <v>3.42</v>
+        <v>4.9</v>
       </c>
       <c r="P15" t="n">
-        <v>4.8</v>
+        <v>6.94</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="S15" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>3.33</v>
+        <v>1.97</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.55</v>
+        <v>5.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>1.38</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.82</v>
+        <v>1.98</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>1.68</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2895,7 +2895,7 @@
         <v>0</v>
       </c>
       <c r="AU15" s="3" t="n">
-        <v>46190.625</v>
+        <v>46190.54166666666</v>
       </c>
     </row>
     <row r="16">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="AU16" s="3" t="n">
-        <v>46190.66666666666</v>
+        <v>46190.58333333334</v>
       </c>
     </row>
     <row r="17">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="AU17" s="3" t="n">
-        <v>46190.83333333334</v>
+        <v>46190.58333333334</v>
       </c>
     </row>
     <row r="18">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,109 +3269,745 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>4.11</v>
+        <v>5.23</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.74</v>
+        <v>2.28</v>
       </c>
       <c r="V18" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.06</v>
+        <v>2.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE18" t="n">
         <v>1.12</v>
       </c>
       <c r="AF18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" s="3" t="n">
+        <v>46190.58333333334</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Gimnasia Jujuy</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Nueva Chicago</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" s="3" t="n">
+        <v>46190.625</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Oakland Roots</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Birmingham Legion</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" s="3" t="n">
+        <v>46190.66666666666</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Indy Eleven</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Brooklyn FC</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P21" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" s="3" t="n">
+        <v>46190.83333333334</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Tulsa Roughnecks</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Monterey Bay</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P22" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF22" t="n">
         <v>1.71</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AG22" t="n">
         <v>1.95</v>
       </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18" t="n">
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22" t="n">
         <v>1.22</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AK22" t="n">
         <v>1.91</v>
       </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" s="3" t="n">
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" s="3" t="n">
         <v>46190.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -728,16 +728,16 @@
         <v>1.35</v>
       </c>
       <c r="O2" t="n">
-        <v>4.62</v>
+        <v>4.15</v>
       </c>
       <c r="P2" t="n">
-        <v>9.25</v>
+        <v>7.35</v>
       </c>
       <c r="Q2" t="n">
         <v>1.83</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S2" t="n">
         <v>1.3</v>
@@ -758,10 +758,10 @@
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="AA2" t="n">
         <v>1.84</v>
@@ -770,19 +770,19 @@
         <v>1.86</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,80 +884,80 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.2</v>
+        <v>2.08</v>
       </c>
       <c r="R3" t="n">
-        <v>2.43</v>
+        <v>2.22</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U3" t="n">
-        <v>2.18</v>
+        <v>2.63</v>
       </c>
       <c r="V3" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="AB3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK3" t="n">
         <v>2.23</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.15</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.26</v>
+        <v>6.43</v>
       </c>
       <c r="O4" t="n">
-        <v>2.88</v>
+        <v>3.19</v>
       </c>
       <c r="P4" t="n">
-        <v>3.11</v>
+        <v>1.56</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>6.43</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.89</v>
+        <v>4.86</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>4.05</v>
       </c>
       <c r="P6" t="n">
-        <v>4.24</v>
+        <v>1.54</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="O7" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="P7" t="n">
-        <v>3.17</v>
+        <v>3.11</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.69</v>
+        <v>1.89</v>
       </c>
       <c r="O8" t="n">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="P8" t="n">
-        <v>4.43</v>
+        <v>4.24</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1712,31 +1712,31 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.38</v>
+        <v>1.46</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="P11" t="n">
-        <v>2.65</v>
+        <v>6.16</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2189,31 +2189,31 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.42</v>
+        <v>2.25</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>9.15</v>
+        <v>1.53</v>
       </c>
       <c r="O12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S12" t="n">
         <v>1.23</v>
       </c>
-      <c r="Q12" t="n">
-        <v>7</v>
-      </c>
-      <c r="R12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U12" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="V12" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="W12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.23</v>
       </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AF12" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.05</v>
+        <v>2.3</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,80 +2474,80 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="O13" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="P13" t="n">
-        <v>6.16</v>
+        <v>6</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.72</v>
+        <v>1.45</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.94</v>
+        <v>2.75</v>
       </c>
       <c r="AC13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK13" t="n">
         <v>2.8</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>2.25</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="O14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T14" t="n">
         <v>4.2</v>
       </c>
-      <c r="P14" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
       <c r="U14" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="V14" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="W14" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AA14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.42</v>
       </c>
-      <c r="AB14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AF14" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.35</v>
+        <v>1.02</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.35</v>
+        <v>2.3</v>
       </c>
       <c r="O15" t="n">
-        <v>4.9</v>
+        <v>3.34</v>
       </c>
       <c r="P15" t="n">
-        <v>6.94</v>
+        <v>2.64</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.74</v>
+        <v>2.89</v>
       </c>
       <c r="R15" t="n">
-        <v>2.88</v>
+        <v>2.12</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U15" t="n">
-        <v>1.97</v>
+        <v>2.63</v>
       </c>
       <c r="V15" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="W15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.19</v>
       </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Z15" t="n">
-        <v>5.6</v>
+        <v>3.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.38</v>
+        <v>1.86</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.98</v>
+        <v>2.78</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.68</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.9</v>
+        <v>1.48</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2951,19 +2951,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -2972,10 +2972,10 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -2984,31 +2984,31 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3131,10 +3131,10 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -3143,31 +3143,31 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,19 +3269,19 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.53</v>
+        <v>3.89</v>
       </c>
       <c r="O18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q18" t="n">
         <v>4</v>
       </c>
-      <c r="P18" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.95</v>
-      </c>
       <c r="R18" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3290,10 +3290,10 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V18" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -3302,31 +3302,31 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AB18" t="n">
         <v>2.04</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.18</v>
+        <v>1.18</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3431,7 +3431,7 @@
         <v>1.64</v>
       </c>
       <c r="O19" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="P19" t="n">
         <v>4.8</v>
@@ -3479,7 +3479,7 @@
         <v>1.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF19" t="n">
         <v>2</v>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="O20" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P20" t="n">
-        <v>3.3</v>
+        <v>2.81</v>
       </c>
       <c r="Q20" t="n">
         <v>2.48</v>
@@ -3602,7 +3602,7 @@
         <v>2.33</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T20" t="n">
         <v>3.2</v>
@@ -3629,7 +3629,7 @@
         <v>1.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC20" t="n">
         <v>2.73</v>
@@ -3657,7 +3657,7 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK20" t="n">
         <v>1.62</v>
@@ -3746,31 +3746,31 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="O21" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P21" t="n">
-        <v>4.15</v>
+        <v>3.95</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="R21" t="n">
         <v>2.38</v>
       </c>
       <c r="S21" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T21" t="n">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="U21" t="n">
-        <v>2.27</v>
+        <v>2.41</v>
       </c>
       <c r="V21" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W21" t="n">
         <v>1.13</v>
@@ -3779,31 +3779,31 @@
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.2</v>
+        <v>4.49</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AE21" t="n">
         <v>1.15</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="O22" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="P22" t="n">
-        <v>4.11</v>
+        <v>3.23</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S22" t="n">
         <v>1.33</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="U22" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="V22" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X22" t="n">
         <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB22" t="n">
         <v>1.95</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF22" t="n">
         <v>1.71</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA3" t="n">
         <v>1.53</v>
       </c>
-      <c r="O3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="P3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AB3" t="n">
-        <v>2.05</v>
+        <v>2.31</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.8</v>
+        <v>2.28</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.23</v>
+        <v>1.11</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>6.43</v>
+        <v>2.26</v>
       </c>
       <c r="O4" t="n">
-        <v>3.19</v>
+        <v>2.88</v>
       </c>
       <c r="P4" t="n">
-        <v>1.56</v>
+        <v>3.11</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.86</v>
+        <v>2.28</v>
       </c>
       <c r="O6" t="n">
-        <v>4.05</v>
+        <v>2.8</v>
       </c>
       <c r="P6" t="n">
-        <v>1.54</v>
+        <v>3.17</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.89</v>
+        <v>1.53</v>
       </c>
       <c r="O8" t="n">
-        <v>2.9</v>
+        <v>3.85</v>
       </c>
       <c r="P8" t="n">
-        <v>4.24</v>
+        <v>4.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.28</v>
+        <v>6.43</v>
       </c>
       <c r="O9" t="n">
-        <v>2.8</v>
+        <v>3.19</v>
       </c>
       <c r="P9" t="n">
-        <v>3.17</v>
+        <v>1.56</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.53</v>
+        <v>8</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="P12" t="n">
-        <v>4.8</v>
+        <v>1.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.97</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="S12" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="T12" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="U12" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="V12" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="W12" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.3</v>
+        <v>1.02</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="O13" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="R13" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="S13" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T13" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U13" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="V13" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="W13" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>8</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>5.5</v>
+        <v>3.34</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25</v>
+        <v>2.64</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.050000000000001</v>
+        <v>2.89</v>
       </c>
       <c r="R14" t="n">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="S14" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="T14" t="n">
-        <v>4.2</v>
+        <v>2.97</v>
       </c>
       <c r="U14" t="n">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="V14" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="W14" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.9</v>
+        <v>3.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.3</v>
+        <v>1.86</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.75</v>
+        <v>2.78</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.95</v>
+        <v>1.28</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.42</v>
+        <v>1.09</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.11</v>
+        <v>1.34</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.3</v>
+        <v>1.36</v>
       </c>
       <c r="O15" t="n">
-        <v>3.34</v>
+        <v>4.6</v>
       </c>
       <c r="P15" t="n">
-        <v>2.64</v>
+        <v>6</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.89</v>
+        <v>1.81</v>
       </c>
       <c r="R15" t="n">
-        <v>2.12</v>
+        <v>2.65</v>
       </c>
       <c r="S15" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T15" t="n">
-        <v>2.97</v>
+        <v>3.6</v>
       </c>
       <c r="U15" t="n">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="V15" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.25</v>
+        <v>5.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.86</v>
+        <v>1.45</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.78</v>
+        <v>2.05</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.09</v>
+        <v>1.27</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.48</v>
+        <v>2.8</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,19 +2951,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.35</v>
+        <v>3.89</v>
       </c>
       <c r="O16" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>7.55</v>
+        <v>1.82</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.76</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>2.63</v>
+        <v>2.33</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -2972,10 +2972,10 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -2984,31 +2984,31 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.89</v>
+        <v>2.15</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.7</v>
+        <v>1.18</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,19 +3269,19 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.89</v>
+        <v>1.35</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="P18" t="n">
-        <v>1.82</v>
+        <v>7.55</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>1.76</v>
       </c>
       <c r="R18" t="n">
-        <v>2.33</v>
+        <v>2.63</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3290,10 +3290,10 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="V18" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -3302,31 +3302,31 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.19</v>
       </c>
-      <c r="Z18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AF18" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.18</v>
+        <v>2.7</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3437,16 +3437,16 @@
         <v>4.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="R19" t="n">
         <v>2.1</v>
       </c>
       <c r="S19" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T19" t="n">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="U19" t="n">
         <v>3.33</v>
@@ -3467,25 +3467,25 @@
         <v>2.55</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AC19" t="n">
         <v>3.82</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF19" t="n">
         <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.26</v>
+        <v>1.53</v>
       </c>
       <c r="O4" t="n">
-        <v>2.88</v>
+        <v>3.85</v>
       </c>
       <c r="P4" t="n">
-        <v>3.11</v>
+        <v>4.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.89</v>
+        <v>6.43</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>3.19</v>
       </c>
       <c r="P5" t="n">
-        <v>4.24</v>
+        <v>1.56</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.53</v>
+        <v>2.26</v>
       </c>
       <c r="O8" t="n">
-        <v>3.85</v>
+        <v>2.88</v>
       </c>
       <c r="P8" t="n">
-        <v>4.8</v>
+        <v>3.11</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>6.43</v>
+        <v>4.86</v>
       </c>
       <c r="O9" t="n">
-        <v>3.19</v>
+        <v>4.05</v>
       </c>
       <c r="P9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V9" t="n">
         <v>1.56</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="O11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>6.16</v>
+        <v>4.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.94</v>
+        <v>2.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.84</v>
+        <v>2.33</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>8</v>
+        <v>1.36</v>
       </c>
       <c r="O12" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="P12" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="S12" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q12" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="R12" t="n">
-        <v>3</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W12" t="n">
         <v>1.17</v>
       </c>
-      <c r="T12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.02</v>
+        <v>2.8</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.53</v>
+        <v>8</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="P13" t="n">
-        <v>4.8</v>
+        <v>1.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.97</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="S13" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="T13" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="U13" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="V13" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="W13" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.3</v>
+        <v>1.02</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>1.46</v>
       </c>
       <c r="O14" t="n">
-        <v>3.34</v>
+        <v>4.1</v>
       </c>
       <c r="P14" t="n">
-        <v>2.64</v>
+        <v>6.16</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.19</v>
+        <v>1.84</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.34</v>
+        <v>1.16</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.48</v>
+        <v>2.25</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.36</v>
+        <v>2.3</v>
       </c>
       <c r="O15" t="n">
-        <v>4.6</v>
+        <v>3.34</v>
       </c>
       <c r="P15" t="n">
-        <v>6</v>
+        <v>2.64</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.81</v>
+        <v>2.89</v>
       </c>
       <c r="R15" t="n">
-        <v>2.65</v>
+        <v>2.12</v>
       </c>
       <c r="S15" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T15" t="n">
-        <v>3.6</v>
+        <v>2.97</v>
       </c>
       <c r="U15" t="n">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="V15" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="W15" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.6</v>
+        <v>3.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.45</v>
+        <v>1.86</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.05</v>
+        <v>2.78</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.68</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.27</v>
+        <v>1.09</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.8</v>
+        <v>1.48</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,19 +2951,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.89</v>
+        <v>1.53</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>1.82</v>
+        <v>5.23</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>1.95</v>
       </c>
       <c r="R16" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -2972,10 +2972,10 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V16" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -2984,31 +2984,31 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AB16" t="n">
         <v>2.04</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.18</v>
+        <v>2.18</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.53</v>
+        <v>3.89</v>
       </c>
       <c r="O17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q17" t="n">
         <v>4</v>
       </c>
-      <c r="P17" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.95</v>
-      </c>
       <c r="R17" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3131,10 +3131,10 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -3143,31 +3143,31 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AB17" t="n">
         <v>2.04</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.18</v>
+        <v>1.18</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.53</v>
+        <v>2.28</v>
       </c>
       <c r="O4" t="n">
-        <v>3.85</v>
+        <v>2.8</v>
       </c>
       <c r="P4" t="n">
-        <v>4.8</v>
+        <v>3.17</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>6.43</v>
+        <v>1.89</v>
       </c>
       <c r="O5" t="n">
-        <v>3.19</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>1.56</v>
+        <v>4.24</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.28</v>
+        <v>1.53</v>
       </c>
       <c r="O6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC6" t="n">
         <v>2.8</v>
       </c>
-      <c r="P6" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.89</v>
+        <v>2.26</v>
       </c>
       <c r="O7" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="P7" t="n">
-        <v>4.24</v>
+        <v>3.11</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.53</v>
+        <v>8</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="P11" t="n">
-        <v>4.8</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.97</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="S11" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="T11" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="U11" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="V11" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="W11" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.3</v>
+        <v>1.02</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>8</v>
+        <v>1.46</v>
       </c>
       <c r="O13" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="P13" t="n">
-        <v>1.25</v>
+        <v>6.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.050000000000001</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.9</v>
+        <v>3.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.2</v>
+        <v>1.94</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.75</v>
+        <v>2.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.95</v>
+        <v>1.35</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.42</v>
+        <v>1.12</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.18</v>
+        <v>1.84</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.02</v>
+        <v>2.25</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="O14" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>6.16</v>
+        <v>4.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.94</v>
+        <v>2.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.84</v>
+        <v>2.33</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,19 +2951,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.53</v>
+        <v>3.89</v>
       </c>
       <c r="O16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q16" t="n">
         <v>4</v>
       </c>
-      <c r="P16" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.95</v>
-      </c>
       <c r="R16" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -2972,10 +2972,10 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -2984,31 +2984,31 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AB16" t="n">
         <v>2.04</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.18</v>
+        <v>1.18</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.89</v>
+        <v>1.53</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>1.82</v>
+        <v>5.23</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>1.95</v>
       </c>
       <c r="R17" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3131,10 +3131,10 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V17" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -3143,31 +3143,31 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AB17" t="n">
         <v>2.04</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.18</v>
+        <v>2.18</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="O2" t="n">
-        <v>4.15</v>
+        <v>4.45</v>
       </c>
       <c r="P2" t="n">
-        <v>7.35</v>
+        <v>7.9</v>
       </c>
       <c r="Q2" t="n">
         <v>1.83</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S2" t="n">
         <v>1.3</v>
@@ -746,40 +746,40 @@
         <v>3.2</v>
       </c>
       <c r="U2" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="V2" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="AG2" t="n">
         <v>1.62</v>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AK2" t="n">
         <v>3.03</v>
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>6.43</v>
+        <v>1.55</v>
       </c>
       <c r="O3" t="n">
-        <v>3.19</v>
+        <v>3.9</v>
       </c>
       <c r="P3" t="n">
-        <v>1.56</v>
+        <v>4.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC4" t="n">
         <v>2.28</v>
       </c>
-      <c r="O4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P4" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.53</v>
+        <v>6.43</v>
       </c>
       <c r="O6" t="n">
-        <v>3.85</v>
+        <v>3.19</v>
       </c>
       <c r="P6" t="n">
-        <v>4.8</v>
+        <v>1.56</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.26</v>
+        <v>1.89</v>
       </c>
       <c r="O7" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="P7" t="n">
-        <v>3.11</v>
+        <v>4.24</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.86</v>
+        <v>2.28</v>
       </c>
       <c r="O9" t="n">
-        <v>4.05</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
-        <v>1.54</v>
+        <v>3.17</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="O10" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P10" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="Q10" t="n">
         <v>2.95</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>8</v>
+        <v>1.36</v>
       </c>
       <c r="O11" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>7</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.050000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="S11" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="T11" t="n">
-        <v>4.2</v>
+        <v>3.58</v>
       </c>
       <c r="U11" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="V11" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.3</v>
       </c>
-      <c r="AB11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.02</v>
+        <v>3.1</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="O12" t="n">
-        <v>4.6</v>
+        <v>4.05</v>
       </c>
       <c r="P12" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z12" t="n">
         <v>3.6</v>
       </c>
-      <c r="U12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>5.6</v>
-      </c>
       <c r="AA12" t="n">
-        <v>1.45</v>
+        <v>1.72</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.75</v>
+        <v>1.94</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.68</v>
+        <v>1.35</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="O13" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>6.16</v>
+        <v>4.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.94</v>
+        <v>2.63</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.8</v>
+        <v>2.14</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.35</v>
+        <v>1.63</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>1.49</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.84</v>
+        <v>2.33</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.97</v>
+        <v>2.89</v>
       </c>
       <c r="R14" t="n">
-        <v>2.6</v>
+        <v>2.12</v>
       </c>
       <c r="S14" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="T14" t="n">
-        <v>3.75</v>
+        <v>2.97</v>
       </c>
       <c r="U14" t="n">
-        <v>2.02</v>
+        <v>2.63</v>
       </c>
       <c r="V14" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="W14" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.4</v>
+        <v>1.78</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="O15" t="n">
-        <v>3.34</v>
+        <v>5.7</v>
       </c>
       <c r="P15" t="n">
-        <v>2.64</v>
+        <v>1.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.89</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="S15" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="T15" t="n">
-        <v>2.97</v>
+        <v>5</v>
       </c>
       <c r="U15" t="n">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="V15" t="n">
-        <v>1.44</v>
+        <v>1.79</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.25</v>
+        <v>6.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.86</v>
+        <v>1.3</v>
       </c>
       <c r="AB15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AG15" t="n">
         <v>2.1</v>
       </c>
-      <c r="AC15" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE15" t="n">
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.09</v>
       </c>
-      <c r="AF15" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AK15" t="n">
-        <v>1.48</v>
+        <v>1.05</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,19 +2951,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.89</v>
+        <v>1.35</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="P16" t="n">
-        <v>1.82</v>
+        <v>7.55</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>1.76</v>
       </c>
       <c r="R16" t="n">
-        <v>2.33</v>
+        <v>2.63</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -2972,10 +2972,10 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="V16" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -2984,31 +2984,31 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.19</v>
       </c>
-      <c r="Z16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AF16" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.18</v>
+        <v>2.7</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.53</v>
+        <v>3.89</v>
       </c>
       <c r="O17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q17" t="n">
         <v>4</v>
       </c>
-      <c r="P17" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.95</v>
-      </c>
       <c r="R17" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3131,10 +3131,10 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -3143,31 +3143,31 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AB17" t="n">
         <v>2.04</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.18</v>
+        <v>1.18</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,19 +3269,19 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="O18" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>7.55</v>
+        <v>5.23</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="R18" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3290,10 +3290,10 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="V18" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -3305,28 +3305,28 @@
         <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.7</v>
+        <v>2.18</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3428,25 +3428,25 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="O19" t="n">
         <v>3.3</v>
       </c>
       <c r="P19" t="n">
-        <v>4.8</v>
+        <v>5.13</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="R19" t="n">
         <v>2.1</v>
       </c>
       <c r="S19" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T19" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="U19" t="n">
         <v>3.33</v>
@@ -3461,31 +3461,31 @@
         <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.55</v>
+        <v>2.76</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.82</v>
+        <v>3.86</v>
       </c>
       <c r="AD19" t="n">
         <v>1.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF19" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="O3" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>4.58</v>
+        <v>7.31</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>6.43</v>
+        <v>1.55</v>
       </c>
       <c r="O6" t="n">
-        <v>3.19</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>1.56</v>
+        <v>4.58</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.89</v>
+        <v>2.45</v>
       </c>
       <c r="O7" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P7" t="n">
-        <v>4.24</v>
+        <v>3.11</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="O8" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="P8" t="n">
-        <v>3.11</v>
+        <v>3.17</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.36</v>
+        <v>7.5</v>
       </c>
       <c r="O11" t="n">
-        <v>4.75</v>
+        <v>5.7</v>
       </c>
       <c r="P11" t="n">
-        <v>7</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC11" t="n">
         <v>1.8</v>
       </c>
-      <c r="R11" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
+      <c r="AD11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.09</v>
       </c>
-      <c r="Z11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AK11" t="n">
-        <v>3.1</v>
+        <v>1.05</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>1.36</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="P14" t="n">
-        <v>2.6</v>
+        <v>7</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.89</v>
+        <v>1.8</v>
       </c>
       <c r="R14" t="n">
-        <v>2.12</v>
+        <v>2.57</v>
       </c>
       <c r="S14" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="T14" t="n">
-        <v>2.97</v>
+        <v>3.58</v>
       </c>
       <c r="U14" t="n">
-        <v>2.63</v>
+        <v>2.07</v>
       </c>
       <c r="V14" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.78</v>
+        <v>2.88</v>
       </c>
       <c r="AC14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK14" t="n">
         <v>3.1</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.48</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="O15" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="P15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q15" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="R15" t="n">
+      <c r="Z15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC15" t="n">
         <v>3.1</v>
       </c>
-      <c r="S15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T15" t="n">
-        <v>5</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.37</v>
+        <v>1.09</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.09</v>
+        <v>1.34</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.05</v>
+        <v>1.48</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,19 +2951,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="O16" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>7.55</v>
+        <v>5.23</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="R16" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -2972,10 +2972,10 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="V16" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -2987,28 +2987,28 @@
         <v>1.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.7</v>
+        <v>2.18</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.89</v>
+        <v>1.35</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="P17" t="n">
-        <v>1.82</v>
+        <v>7.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>1.76</v>
       </c>
       <c r="R17" t="n">
-        <v>2.33</v>
+        <v>2.63</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3131,10 +3131,10 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="V17" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -3143,31 +3143,31 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.19</v>
       </c>
-      <c r="Z17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AF17" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.18</v>
+        <v>2.7</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,19 +3269,19 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.53</v>
+        <v>3.89</v>
       </c>
       <c r="O18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q18" t="n">
         <v>4</v>
       </c>
-      <c r="P18" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.95</v>
-      </c>
       <c r="R18" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3290,10 +3290,10 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V18" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -3302,31 +3302,31 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AB18" t="n">
         <v>2.04</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.18</v>
+        <v>1.18</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3434,58 +3434,58 @@
         <v>3.3</v>
       </c>
       <c r="P19" t="n">
-        <v>5.13</v>
+        <v>5.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T19" t="n">
         <v>2.47</v>
       </c>
       <c r="U19" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X19" t="n">
         <v>1.05</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.86</v>
+        <v>3.76</v>
       </c>
       <c r="AD19" t="n">
         <v>1.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3599,19 +3599,19 @@
         <v>2.48</v>
       </c>
       <c r="R20" t="n">
-        <v>2.33</v>
+        <v>2.22</v>
       </c>
       <c r="S20" t="n">
         <v>1.28</v>
       </c>
       <c r="T20" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="U20" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="V20" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W20" t="n">
         <v>1.08</v>
@@ -3620,7 +3620,7 @@
         <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z20" t="n">
         <v>3.9</v>
@@ -3638,13 +3638,13 @@
         <v>1.37</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.32</v>
+        <v>2.19</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="O21" t="n">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="P21" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="Q21" t="n">
         <v>2.13</v>
@@ -3767,7 +3767,7 @@
         <v>3.28</v>
       </c>
       <c r="U21" t="n">
-        <v>2.41</v>
+        <v>2.31</v>
       </c>
       <c r="V21" t="n">
         <v>1.54</v>
@@ -3779,16 +3779,16 @@
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.49</v>
+        <v>4</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="AC21" t="n">
         <v>2.55</v>
@@ -3911,7 +3911,7 @@
         <v>3.18</v>
       </c>
       <c r="P22" t="n">
-        <v>3.23</v>
+        <v>3.3</v>
       </c>
       <c r="Q22" t="n">
         <v>2.5</v>
@@ -3926,7 +3926,7 @@
         <v>3.04</v>
       </c>
       <c r="U22" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="V22" t="n">
         <v>1.4</v>
@@ -3944,13 +3944,13 @@
         <v>3.34</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.05</v>
+        <v>3.16</v>
       </c>
       <c r="AD22" t="n">
         <v>1.28</v>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK22" t="n">
         <v>1.76</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="O8" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="P8" t="n">
-        <v>3.17</v>
+        <v>3.11</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V12" t="n">
         <v>1.44</v>
       </c>
-      <c r="O12" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="P12" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.84</v>
+        <v>2.19</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.25</v>
+        <v>1.48</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="P15" t="n">
-        <v>2.6</v>
+        <v>5.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.19</v>
+        <v>1.84</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.34</v>
+        <v>1.07</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.48</v>
+        <v>2.25</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,19 +2951,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="P16" t="n">
-        <v>5.23</v>
+        <v>7.55</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="R16" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -2972,10 +2972,10 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="V16" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -2987,44 +2987,44 @@
         <v>1.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AE16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
         <v>1.12</v>
       </c>
-      <c r="AF16" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AK16" t="n">
-        <v>2.18</v>
+        <v>2.7</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.35</v>
+        <v>3.89</v>
       </c>
       <c r="O17" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="P17" t="n">
-        <v>7.55</v>
+        <v>1.82</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.76</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>2.63</v>
+        <v>2.33</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3131,10 +3131,10 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -3143,31 +3143,31 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.89</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.7</v>
+        <v>1.18</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,19 +3269,19 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.89</v>
+        <v>1.53</v>
       </c>
       <c r="O18" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>1.82</v>
+        <v>5.23</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>1.95</v>
       </c>
       <c r="R18" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3290,10 +3290,10 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V18" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -3302,31 +3302,31 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AB18" t="n">
         <v>2.04</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.18</v>
+        <v>2.18</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.51</v>
+        <v>2.45</v>
       </c>
       <c r="O3" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="P3" t="n">
-        <v>7.31</v>
+        <v>3.11</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.11</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>6.43</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="P5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF5" t="n">
         <v>1.67</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="P6" t="n">
-        <v>4.58</v>
+        <v>7.31</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.45</v>
+        <v>6.43</v>
       </c>
       <c r="O8" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="P8" t="n">
-        <v>3.11</v>
+        <v>1.67</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="P12" t="n">
-        <v>2.6</v>
+        <v>5.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.19</v>
+        <v>1.84</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.34</v>
+        <v>1.07</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.48</v>
+        <v>2.25</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.36</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
-        <v>7</v>
+        <v>2.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.8</v>
+        <v>2.89</v>
       </c>
       <c r="R14" t="n">
-        <v>2.57</v>
+        <v>2.12</v>
       </c>
       <c r="S14" t="n">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="T14" t="n">
-        <v>3.58</v>
+        <v>2.97</v>
       </c>
       <c r="U14" t="n">
-        <v>2.07</v>
+        <v>2.63</v>
       </c>
       <c r="V14" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="W14" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.09</v>
       </c>
-      <c r="Z14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AF14" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.1</v>
+        <v>1.48</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="O15" t="n">
-        <v>4.05</v>
+        <v>4.75</v>
       </c>
       <c r="P15" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.94</v>
+        <v>2.88</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.8</v>
+        <v>2.05</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.84</v>
+        <v>2.16</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,19 +2951,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.35</v>
+        <v>3.89</v>
       </c>
       <c r="O16" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>7.55</v>
+        <v>1.82</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.76</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>2.63</v>
+        <v>2.33</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -2972,10 +2972,10 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="V16" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -2984,31 +2984,31 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.89</v>
+        <v>2.15</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.7</v>
+        <v>1.18</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.89</v>
+        <v>1.53</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>1.82</v>
+        <v>5.23</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>1.95</v>
       </c>
       <c r="R17" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3131,10 +3131,10 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V17" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -3143,31 +3143,31 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AB17" t="n">
         <v>2.04</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.18</v>
+        <v>2.18</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,19 +3269,19 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="P18" t="n">
-        <v>5.23</v>
+        <v>7.55</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="R18" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3290,10 +3290,10 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="V18" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -3305,44 +3305,44 @@
         <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AE18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
         <v>1.12</v>
       </c>
-      <c r="AF18" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AK18" t="n">
-        <v>2.18</v>
+        <v>2.7</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="O2" t="n">
-        <v>4.45</v>
+        <v>4.65</v>
       </c>
       <c r="P2" t="n">
-        <v>7.9</v>
+        <v>9.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="R2" t="n">
         <v>2.38</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T2" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="U2" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W2" t="n">
         <v>1.08</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.45</v>
+        <v>6.43</v>
       </c>
       <c r="O3" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>3.11</v>
+        <v>1.67</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>7.31</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>1.55</v>
       </c>
       <c r="O5" t="n">
         <v>3.9</v>
       </c>
       <c r="P5" t="n">
-        <v>1.61</v>
+        <v>4.58</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.11</v>
+        <v>2.07</v>
       </c>
       <c r="R5" t="n">
-        <v>2.36</v>
+        <v>2.23</v>
       </c>
       <c r="S5" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T5" t="n">
-        <v>3.5</v>
+        <v>2.97</v>
       </c>
       <c r="U5" t="n">
-        <v>2.26</v>
+        <v>2.53</v>
       </c>
       <c r="V5" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="W5" t="n">
         <v>1.11</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.45</v>
+        <v>3.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.28</v>
+        <v>2.78</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF5" t="n">
         <v>1.67</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.1</v>
+        <v>1.93</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.51</v>
+        <v>2.18</v>
       </c>
       <c r="O6" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="P6" t="n">
-        <v>7.31</v>
+        <v>3.17</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>6.43</v>
+        <v>2.45</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="P8" t="n">
-        <v>1.67</v>
+        <v>3.11</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.18</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="P9" t="n">
-        <v>3.17</v>
+        <v>1.61</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2000,61 +2000,61 @@
         <v>2.45</v>
       </c>
       <c r="O10" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
         <v>2.58</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.95</v>
+        <v>3.06</v>
       </c>
       <c r="R10" t="n">
         <v>2.14</v>
       </c>
       <c r="S10" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T10" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y10" t="n">
         <v>1.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>7.5</v>
+        <v>1.53</v>
       </c>
       <c r="O11" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>4.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.300000000000001</v>
+        <v>1.94</v>
       </c>
       <c r="R11" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="S11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="W11" t="n">
         <v>1.14</v>
       </c>
-      <c r="T11" t="n">
-        <v>5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.18</v>
-      </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.05</v>
+        <v>2.35</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V12" t="n">
         <v>1.44</v>
       </c>
-      <c r="O12" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="P12" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.84</v>
+        <v>2.19</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.25</v>
+        <v>1.48</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="P13" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="R13" t="n">
-        <v>2.7</v>
+        <v>2.57</v>
       </c>
       <c r="S13" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="T13" t="n">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="U13" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="V13" t="n">
         <v>1.67</v>
       </c>
       <c r="W13" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z13" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.33</v>
+        <v>2.16</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R14" t="n">
         <v>2.3</v>
       </c>
-      <c r="O14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.12</v>
-      </c>
       <c r="S14" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="T14" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V14" t="n">
         <v>1.44</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.58</v>
+        <v>1.86</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.19</v>
+        <v>1.81</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.34</v>
+        <v>1.07</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.48</v>
+        <v>2.4</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.36</v>
+        <v>7.5</v>
       </c>
       <c r="O15" t="n">
-        <v>4.75</v>
+        <v>5.7</v>
       </c>
       <c r="P15" t="n">
-        <v>7</v>
+        <v>1.25</v>
       </c>
       <c r="Q15" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="R15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T15" t="n">
+        <v>5</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC15" t="n">
         <v>1.8</v>
       </c>
-      <c r="R15" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
+      <c r="AD15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.09</v>
       </c>
-      <c r="Z15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AK15" t="n">
-        <v>3.1</v>
+        <v>1.05</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="P17" t="n">
-        <v>5.23</v>
+        <v>7.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="R17" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3131,10 +3131,10 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="V17" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -3146,44 +3146,44 @@
         <v>1.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AE17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.12</v>
       </c>
-      <c r="AF17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AK17" t="n">
-        <v>2.18</v>
+        <v>2.7</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,19 +3269,19 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="O18" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>7.55</v>
+        <v>5.23</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="R18" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3290,10 +3290,10 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="V18" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -3305,28 +3305,28 @@
         <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.7</v>
+        <v>2.18</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>6.43</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="P3" t="n">
-        <v>1.67</v>
+        <v>3.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.51</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="P4" t="n">
-        <v>7.31</v>
+        <v>3.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="O5" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>4.58</v>
+        <v>5.25</v>
       </c>
       <c r="Q5" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK5" t="n">
         <v>2.07</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.93</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.18</v>
+        <v>1.53</v>
       </c>
       <c r="O6" t="n">
-        <v>2.8</v>
+        <v>3.82</v>
       </c>
       <c r="P6" t="n">
-        <v>3.17</v>
+        <v>5.77</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.45</v>
+        <v>4.53</v>
       </c>
       <c r="O8" t="n">
-        <v>2.95</v>
+        <v>3.9</v>
       </c>
       <c r="P8" t="n">
-        <v>3.11</v>
+        <v>1.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>1.84</v>
       </c>
       <c r="O9" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="P9" t="n">
-        <v>1.61</v>
+        <v>4.07</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.11</v>
+        <v>2.51</v>
       </c>
       <c r="R9" t="n">
-        <v>2.36</v>
+        <v>1.96</v>
       </c>
       <c r="S9" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>2.47</v>
       </c>
       <c r="U9" t="n">
-        <v>2.26</v>
+        <v>3.08</v>
       </c>
       <c r="V9" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.45</v>
+        <v>2.78</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.57</v>
+        <v>2.13</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.38</v>
+        <v>1.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.28</v>
+        <v>3.82</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.5</v>
+        <v>1.19</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.1</v>
+        <v>1.78</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,34 +1997,34 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="P10" t="n">
         <v>2.58</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.06</v>
+        <v>3.18</v>
       </c>
       <c r="R10" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="S10" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="U10" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="V10" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W10" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X10" t="n">
         <v>1.04</v>
@@ -2036,25 +2036,25 @@
         <v>3.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>1.27</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
         <v>4.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="R11" t="n">
-        <v>2.7</v>
+        <v>2.12</v>
       </c>
       <c r="S11" t="n">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="T11" t="n">
-        <v>3.42</v>
+        <v>2.81</v>
       </c>
       <c r="U11" t="n">
-        <v>2.02</v>
+        <v>2.85</v>
       </c>
       <c r="V11" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="Z11" t="n">
-        <v>6</v>
+        <v>3.14</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.47</v>
+        <v>1.91</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.63</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.14</v>
+        <v>3.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.63</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.49</v>
+        <v>1.91</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.33</v>
+        <v>1.77</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>1.17</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2318,16 +2318,16 @@
         <v>2.3</v>
       </c>
       <c r="O12" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="R12" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="S12" t="n">
         <v>1.31</v>
@@ -2348,31 +2348,31 @@
         <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="AA12" t="n">
         <v>1.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE12" t="n">
         <v>1.09</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AK12" t="n">
         <v>1.48</v>
@@ -2477,61 +2477,61 @@
         <v>1.36</v>
       </c>
       <c r="O13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P13" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z13" t="n">
         <v>4.75</v>
       </c>
-      <c r="P13" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="V13" t="n">
+      <c r="AA13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF13" t="n">
         <v>1.67</v>
       </c>
-      <c r="W13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AG13" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>1.13</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="O14" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="P14" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z14" t="n">
         <v>5.5</v>
       </c>
-      <c r="Q14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AA14" t="n">
-        <v>1.8</v>
+        <v>1.51</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.94</v>
+        <v>2.35</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.92</v>
+        <v>2.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AK14" t="n">
         <v>2.4</v>
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="O15" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="P15" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.300000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="R15" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="S15" t="n">
         <v>1.14</v>
       </c>
       <c r="T15" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="V15" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="W15" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.09</v>
+        <v>4.85</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.89</v>
+        <v>1.49</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="P16" t="n">
-        <v>1.82</v>
+        <v>4.97</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>1.91</v>
       </c>
       <c r="R16" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U16" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
         <v>3.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.18</v>
+        <v>2.4</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.35</v>
+        <v>5.05</v>
       </c>
       <c r="O17" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="P17" t="n">
-        <v>7.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.76</v>
+        <v>4.5</v>
       </c>
       <c r="R17" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="U17" t="n">
-        <v>2.14</v>
+        <v>2.64</v>
       </c>
       <c r="V17" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.4</v>
+        <v>3.58</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.28</v>
+        <v>1.9</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.28</v>
+        <v>2.97</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK17" t="n">
         <v>1.12</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>2.7</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="P18" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AA18" t="n">
         <v>1.53</v>
       </c>
-      <c r="O18" t="n">
-        <v>4</v>
-      </c>
-      <c r="P18" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AB18" t="n">
-        <v>2.04</v>
+        <v>2.35</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.18</v>
+        <v>2.97</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="O19" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="P19" t="n">
-        <v>5.25</v>
+        <v>4.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="R19" t="n">
         <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T19" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="V19" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W19" t="n">
         <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
         <v>1.62</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.76</v>
+        <v>3.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3596,55 +3596,55 @@
         <v>2.81</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="R20" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="S20" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="T20" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="U20" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.9</v>
+        <v>3.79</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="AD20" t="n">
         <v>1.37</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.19</v>
+        <v>2.32</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3746,34 +3746,34 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="O21" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="P21" t="n">
-        <v>4.4</v>
+        <v>4.21</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="R21" t="n">
         <v>2.38</v>
       </c>
       <c r="S21" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T21" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="U21" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="V21" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
@@ -3782,29 +3782,29 @@
         <v>1.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AB21" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG21" t="n">
         <v>2.21</v>
       </c>
-      <c r="AC21" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.18</v>
-      </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3908,28 +3908,28 @@
         <v>1.8</v>
       </c>
       <c r="O22" t="n">
-        <v>3.18</v>
+        <v>3.35</v>
       </c>
       <c r="P22" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="R22" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S22" t="n">
         <v>1.33</v>
       </c>
       <c r="T22" t="n">
-        <v>3.04</v>
+        <v>2.91</v>
       </c>
       <c r="U22" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W22" t="n">
         <v>1.05</v>
@@ -3938,7 +3938,7 @@
         <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z22" t="n">
         <v>3.34</v>
@@ -3950,19 +3950,19 @@
         <v>1.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AE22" t="n">
         <v>1.07</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>1.22</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="O4" t="n">
-        <v>2.9</v>
+        <v>3.82</v>
       </c>
       <c r="P4" t="n">
-        <v>3.6</v>
+        <v>5.77</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.63</v>
+        <v>2.07</v>
       </c>
       <c r="R4" t="n">
-        <v>1.87</v>
+        <v>2.19</v>
       </c>
       <c r="S4" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="T4" t="n">
-        <v>2.31</v>
+        <v>2.88</v>
       </c>
       <c r="U4" t="n">
-        <v>3.58</v>
+        <v>2.53</v>
       </c>
       <c r="V4" t="n">
-        <v>1.21</v>
+        <v>1.42</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.41</v>
+        <v>3.95</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.47</v>
+        <v>2.05</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.1</v>
+        <v>2.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.1</v>
+        <v>1.41</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.21</v>
+        <v>1.67</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.58</v>
+        <v>1.88</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="P5" t="n">
-        <v>5.25</v>
+        <v>1.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.29</v>
+        <v>6.1</v>
       </c>
       <c r="R5" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="S5" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="T5" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="U5" t="n">
-        <v>3.32</v>
+        <v>3.7</v>
       </c>
       <c r="V5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.26</v>
       </c>
-      <c r="W5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AK5" t="n">
-        <v>2.07</v>
+        <v>1.11</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,80 +1361,80 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>3.82</v>
+        <v>2.9</v>
       </c>
       <c r="P6" t="n">
-        <v>5.77</v>
+        <v>3.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.07</v>
+        <v>2.63</v>
       </c>
       <c r="R6" t="n">
-        <v>2.19</v>
+        <v>1.87</v>
       </c>
       <c r="S6" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="T6" t="n">
-        <v>2.88</v>
+        <v>2.31</v>
       </c>
       <c r="U6" t="n">
-        <v>2.53</v>
+        <v>3.58</v>
       </c>
       <c r="V6" t="n">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.95</v>
+        <v>2.41</v>
       </c>
       <c r="AA6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>2.3</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.9</v>
+        <v>4.53</v>
       </c>
       <c r="O7" t="n">
-        <v>3.18</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.1</v>
+        <v>5.17</v>
       </c>
       <c r="R7" t="n">
-        <v>1.89</v>
+        <v>2.34</v>
       </c>
       <c r="S7" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="T7" t="n">
-        <v>2.28</v>
+        <v>3.28</v>
       </c>
       <c r="U7" t="n">
-        <v>3.7</v>
+        <v>2.27</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.45</v>
+        <v>4.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.52</v>
+        <v>1.57</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.44</v>
+        <v>2.23</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.2</v>
+        <v>2.35</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.1</v>
+        <v>1.47</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.32</v>
+        <v>1.62</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.53</v>
+        <v>2.12</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AK7" t="n">
         <v>1.11</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.53</v>
+        <v>1.6</v>
       </c>
       <c r="O8" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.55</v>
+        <v>5.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.17</v>
+        <v>2.29</v>
       </c>
       <c r="R8" t="n">
-        <v>2.34</v>
+        <v>1.95</v>
       </c>
       <c r="S8" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="T8" t="n">
-        <v>3.28</v>
+        <v>2.38</v>
       </c>
       <c r="U8" t="n">
-        <v>2.27</v>
+        <v>3.32</v>
       </c>
       <c r="V8" t="n">
-        <v>1.52</v>
+        <v>1.26</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.12</v>
+        <v>1.61</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.11</v>
+        <v>2.07</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.3</v>
+        <v>11</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>6.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.62</v>
+        <v>1.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.9</v>
+        <v>10.8</v>
       </c>
       <c r="R12" t="n">
-        <v>2.11</v>
+        <v>3</v>
       </c>
       <c r="S12" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="T12" t="n">
-        <v>2.97</v>
+        <v>4.3</v>
       </c>
       <c r="U12" t="n">
-        <v>2.63</v>
+        <v>1.83</v>
       </c>
       <c r="V12" t="n">
-        <v>1.44</v>
+        <v>1.93</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y12" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z12" t="n">
-        <v>3.82</v>
+        <v>7.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.73</v>
+        <v>1.29</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.98</v>
+        <v>3.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.88</v>
+        <v>1.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.35</v>
+        <v>2.08</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.24</v>
+        <v>4.85</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.48</v>
+        <v>1.03</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="O13" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="P13" t="n">
-        <v>6.79</v>
+        <v>5.45</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="R13" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="S13" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="T13" t="n">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="V13" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="W13" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="AD13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF13" t="n">
         <v>1.65</v>
       </c>
-      <c r="AE13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AG13" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.45</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="P14" t="n">
-        <v>5.45</v>
+        <v>2.62</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="R14" t="n">
-        <v>2.36</v>
+        <v>2.11</v>
       </c>
       <c r="S14" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="T14" t="n">
-        <v>3.75</v>
+        <v>2.97</v>
       </c>
       <c r="U14" t="n">
-        <v>2.26</v>
+        <v>2.63</v>
       </c>
       <c r="V14" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="W14" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.5</v>
+        <v>3.82</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.35</v>
+        <v>1.98</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.33</v>
+        <v>2.88</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.4</v>
+        <v>1.48</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>11</v>
+        <v>1.36</v>
       </c>
       <c r="O15" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="P15" t="n">
-        <v>1.15</v>
+        <v>6.79</v>
       </c>
       <c r="Q15" t="n">
-        <v>10.8</v>
+        <v>1.85</v>
       </c>
       <c r="R15" t="n">
-        <v>3</v>
+        <v>2.46</v>
       </c>
       <c r="S15" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="T15" t="n">
-        <v>4.3</v>
+        <v>3.34</v>
       </c>
       <c r="U15" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="V15" t="n">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.6</v>
+        <v>4.75</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.5</v>
+        <v>2.37</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.7</v>
+        <v>2.19</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.08</v>
+        <v>1.65</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>4.85</v>
+        <v>1.13</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.03</v>
+        <v>2.88</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,58 +2951,58 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.49</v>
+        <v>5.05</v>
       </c>
       <c r="O16" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="P16" t="n">
-        <v>4.97</v>
+        <v>1.56</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.91</v>
+        <v>4.5</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="V16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.11</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.12</v>
       </c>
       <c r="AF16" t="n">
         <v>1.73</v>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.4</v>
+        <v>1.12</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,58 +3110,58 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>5.05</v>
+        <v>1.49</v>
       </c>
       <c r="O17" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="P17" t="n">
-        <v>1.56</v>
+        <v>4.97</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.5</v>
+        <v>1.91</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="U17" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.97</v>
+        <v>2.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF17" t="n">
         <v>1.73</v>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.12</v>
+        <v>2.4</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>4.53</v>
       </c>
       <c r="O6" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>3.6</v>
+        <v>1.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.63</v>
+        <v>5.17</v>
       </c>
       <c r="R6" t="n">
-        <v>1.87</v>
+        <v>2.34</v>
       </c>
       <c r="S6" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="T6" t="n">
-        <v>2.31</v>
+        <v>3.28</v>
       </c>
       <c r="U6" t="n">
-        <v>3.58</v>
+        <v>2.27</v>
       </c>
       <c r="V6" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.41</v>
+        <v>4.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.47</v>
       </c>
-      <c r="AC6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AE6" t="n">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.21</v>
+        <v>1.62</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.58</v>
+        <v>2.12</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>4.53</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="P7" t="n">
-        <v>1.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.17</v>
+        <v>2.63</v>
       </c>
       <c r="R7" t="n">
-        <v>2.34</v>
+        <v>1.87</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="T7" t="n">
-        <v>3.28</v>
+        <v>2.31</v>
       </c>
       <c r="U7" t="n">
-        <v>2.27</v>
+        <v>3.58</v>
       </c>
       <c r="V7" t="n">
-        <v>1.52</v>
+        <v>1.21</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.3</v>
+        <v>2.41</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.57</v>
+        <v>2.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.23</v>
+        <v>1.47</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.35</v>
+        <v>5.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.47</v>
+        <v>1.1</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.62</v>
+        <v>2.21</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.12</v>
+        <v>1.58</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="P11" t="n">
-        <v>4.8</v>
+        <v>5.45</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="R11" t="n">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="S11" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="T11" t="n">
-        <v>2.81</v>
+        <v>3.75</v>
       </c>
       <c r="U11" t="n">
-        <v>2.85</v>
+        <v>2.26</v>
       </c>
       <c r="V11" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.14</v>
+        <v>5.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.91</v>
+        <v>1.51</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>2.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.4</v>
+        <v>2.33</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="O13" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="P13" t="n">
-        <v>5.45</v>
+        <v>4.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="R13" t="n">
-        <v>2.36</v>
+        <v>2.12</v>
       </c>
       <c r="S13" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="T13" t="n">
-        <v>3.75</v>
+        <v>2.81</v>
       </c>
       <c r="U13" t="n">
-        <v>2.26</v>
+        <v>2.85</v>
       </c>
       <c r="V13" t="n">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="W13" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.5</v>
+        <v>3.14</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.51</v>
+        <v>1.91</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.33</v>
+        <v>3.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.08</v>
+        <v>1.77</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.3</v>
+        <v>1.36</v>
       </c>
       <c r="O14" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.62</v>
+        <v>6.79</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="R14" t="n">
-        <v>2.11</v>
+        <v>2.46</v>
       </c>
       <c r="S14" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="T14" t="n">
-        <v>2.97</v>
+        <v>3.34</v>
       </c>
       <c r="U14" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="V14" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.82</v>
+        <v>4.75</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.98</v>
+        <v>2.37</v>
       </c>
       <c r="AC14" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK14" t="n">
         <v>2.88</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.48</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.36</v>
+        <v>2.3</v>
       </c>
       <c r="O15" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="P15" t="n">
-        <v>6.79</v>
+        <v>2.62</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="R15" t="n">
-        <v>2.46</v>
+        <v>2.11</v>
       </c>
       <c r="S15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.24</v>
       </c>
-      <c r="T15" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AK15" t="n">
-        <v>2.88</v>
+        <v>1.48</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -728,61 +728,61 @@
         <v>1.3</v>
       </c>
       <c r="O2" t="n">
-        <v>4.65</v>
+        <v>4.4</v>
       </c>
       <c r="P2" t="n">
-        <v>9.4</v>
+        <v>7.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R2" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S2" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="T2" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U2" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="V2" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,80 +884,80 @@
         </is>
       </c>
       <c r="N3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="P3" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK3" t="n">
         <v>2.3</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.47</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,80 +1043,80 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="O4" t="n">
-        <v>3.82</v>
+        <v>3.3</v>
       </c>
       <c r="P4" t="n">
-        <v>5.77</v>
+        <v>5.25</v>
       </c>
       <c r="Q4" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK4" t="n">
         <v>2.07</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>2.3</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4.53</v>
+        <v>1.84</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="P6" t="n">
-        <v>1.55</v>
+        <v>4.07</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.17</v>
+        <v>2.51</v>
       </c>
       <c r="R6" t="n">
-        <v>2.34</v>
+        <v>1.96</v>
       </c>
       <c r="S6" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="T6" t="n">
-        <v>3.28</v>
+        <v>2.47</v>
       </c>
       <c r="U6" t="n">
-        <v>2.27</v>
+        <v>3.08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.3</v>
+        <v>2.78</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.57</v>
+        <v>2.13</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.23</v>
+        <v>1.62</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.35</v>
+        <v>3.82</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.62</v>
+        <v>1.92</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.12</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.6</v>
+        <v>4.53</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="P8" t="n">
-        <v>5.25</v>
+        <v>1.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.29</v>
+        <v>5.17</v>
       </c>
       <c r="R8" t="n">
-        <v>1.95</v>
+        <v>2.34</v>
       </c>
       <c r="S8" t="n">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
-        <v>2.38</v>
+        <v>3.28</v>
       </c>
       <c r="U8" t="n">
-        <v>3.32</v>
+        <v>2.27</v>
       </c>
       <c r="V8" t="n">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.66</v>
+        <v>4.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.57</v>
+        <v>2.23</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.2</v>
+        <v>2.35</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.15</v>
+        <v>1.47</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.61</v>
+        <v>2.12</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.07</v>
+        <v>1.11</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="O9" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
-        <v>4.07</v>
+        <v>3.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.51</v>
+        <v>3.17</v>
       </c>
       <c r="R9" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="S9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.44</v>
       </c>
-      <c r="T9" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AC9" t="n">
-        <v>3.82</v>
+        <v>5.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.78</v>
+        <v>1.47</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>11</v>
+        <v>2.3</v>
       </c>
       <c r="O12" t="n">
-        <v>6.5</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>1.15</v>
+        <v>2.62</v>
       </c>
       <c r="Q12" t="n">
-        <v>10.8</v>
+        <v>2.9</v>
       </c>
       <c r="R12" t="n">
-        <v>3</v>
+        <v>2.11</v>
       </c>
       <c r="S12" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="T12" t="n">
-        <v>4.3</v>
+        <v>2.97</v>
       </c>
       <c r="U12" t="n">
-        <v>1.83</v>
+        <v>2.63</v>
       </c>
       <c r="V12" t="n">
-        <v>1.93</v>
+        <v>1.44</v>
       </c>
       <c r="W12" t="n">
-        <v>1.27</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.6</v>
+        <v>3.82</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.29</v>
+        <v>1.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.5</v>
+        <v>1.98</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.08</v>
+        <v>1.35</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.45</v>
+        <v>1.09</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>4.85</v>
+        <v>1.24</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.03</v>
+        <v>1.48</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="P13" t="n">
-        <v>4.8</v>
+        <v>6.79</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="R13" t="n">
-        <v>2.12</v>
+        <v>2.46</v>
       </c>
       <c r="S13" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="T13" t="n">
-        <v>2.81</v>
+        <v>3.34</v>
       </c>
       <c r="U13" t="n">
-        <v>2.85</v>
+        <v>2.1</v>
       </c>
       <c r="V13" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.14</v>
+        <v>4.75</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.91</v>
+        <v>1.46</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>2.37</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.4</v>
+        <v>2.19</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.77</v>
+        <v>2.06</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.36</v>
+        <v>11</v>
       </c>
       <c r="O14" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="P14" t="n">
-        <v>6.79</v>
+        <v>1.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.85</v>
+        <v>10.8</v>
       </c>
       <c r="R14" t="n">
-        <v>2.46</v>
+        <v>3</v>
       </c>
       <c r="S14" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="T14" t="n">
-        <v>3.34</v>
+        <v>4.3</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="V14" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="W14" t="n">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.75</v>
+        <v>7.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.37</v>
+        <v>3.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.19</v>
+        <v>1.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.65</v>
+        <v>2.08</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.13</v>
+        <v>4.85</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.88</v>
+        <v>1.03</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK15" t="n">
         <v>2.3</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.48</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>5.05</v>
+        <v>1.3</v>
       </c>
       <c r="O16" t="n">
-        <v>3.55</v>
+        <v>4.9</v>
       </c>
       <c r="P16" t="n">
-        <v>1.56</v>
+        <v>5.74</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.5</v>
+        <v>1.75</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="S16" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="T16" t="n">
-        <v>2.87</v>
+        <v>3.6</v>
       </c>
       <c r="U16" t="n">
-        <v>2.64</v>
+        <v>2.22</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.58</v>
+        <v>5.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AC16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK16" t="n">
         <v>2.97</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.12</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,80 +3269,80 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.3</v>
+        <v>5.05</v>
       </c>
       <c r="O18" t="n">
-        <v>4.9</v>
+        <v>3.55</v>
       </c>
       <c r="P18" t="n">
-        <v>5.74</v>
+        <v>1.56</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.75</v>
+        <v>4.5</v>
       </c>
       <c r="R18" t="n">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="S18" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="T18" t="n">
-        <v>3.6</v>
+        <v>2.87</v>
       </c>
       <c r="U18" t="n">
-        <v>2.22</v>
+        <v>2.64</v>
       </c>
       <c r="V18" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.2</v>
+        <v>3.58</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.4</v>
+        <v>2.97</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AE18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
         <v>1.18</v>
       </c>
-      <c r="AF18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AK18" t="n">
-        <v>2.97</v>
+        <v>1.12</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,65 +884,65 @@
         </is>
       </c>
       <c r="N3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1.53</v>
       </c>
-      <c r="O3" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="P3" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.3</v>
+        <v>1.11</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="O4" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P4" t="n">
-        <v>5.25</v>
+        <v>3.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.29</v>
+        <v>2.51</v>
       </c>
       <c r="R4" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="S4" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="T4" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="U4" t="n">
-        <v>3.32</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
         <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.2</v>
+        <v>3.84</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,31 +1202,31 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>4.9</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>3.18</v>
+        <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>1.72</v>
+        <v>3.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.1</v>
+        <v>2.63</v>
       </c>
       <c r="R5" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="S5" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="T5" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="U5" t="n">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W5" t="n">
         <v>1.02</v>
@@ -1238,16 +1238,16 @@
         <v>1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AD5" t="n">
         <v>1.1</v>
@@ -1256,10 +1256,10 @@
         <v>1.02</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="O6" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="P6" t="n">
-        <v>4.07</v>
+        <v>3.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.51</v>
+        <v>3.17</v>
       </c>
       <c r="R6" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="S6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB6" t="n">
         <v>1.44</v>
       </c>
-      <c r="T6" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AC6" t="n">
-        <v>3.82</v>
+        <v>5.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.78</v>
+        <v>1.47</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="O7" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="R7" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="S7" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="T7" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="U7" t="n">
-        <v>3.58</v>
+        <v>3.32</v>
       </c>
       <c r="V7" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.41</v>
+        <v>2.66</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4.53</v>
+        <v>1.48</v>
       </c>
       <c r="O8" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>1.55</v>
+        <v>5.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.17</v>
+        <v>1.95</v>
       </c>
       <c r="R8" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="S8" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T8" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="U8" t="n">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="V8" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.35</v>
+        <v>2.81</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.11</v>
+        <v>2.4</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="P9" t="n">
-        <v>3.1</v>
+        <v>1.68</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.17</v>
+        <v>4.33</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="S9" t="n">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="T9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB9" t="n">
         <v>2.2</v>
       </c>
-      <c r="U9" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="V9" t="n">
+      <c r="AC9" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.2</v>
       </c>
-      <c r="W9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AF9" t="n">
-        <v>2.12</v>
+        <v>1.52</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.63</v>
+        <v>2.2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.47</v>
+        <v>1.17</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,31 +1997,31 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="O10" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="U10" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="V10" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W10" t="n">
         <v>1.07</v>
@@ -2030,31 +2030,31 @@
         <v>1.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.45</v>
+        <v>10.52</v>
       </c>
       <c r="O11" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="P11" t="n">
-        <v>5.45</v>
+        <v>1.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.95</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>2.36</v>
+        <v>3.28</v>
       </c>
       <c r="S11" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="T11" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="U11" t="n">
-        <v>2.26</v>
+        <v>1.87</v>
       </c>
       <c r="V11" t="n">
-        <v>1.56</v>
+        <v>1.91</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.5</v>
+        <v>7.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.35</v>
+        <v>3.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.33</v>
+        <v>1.65</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.08</v>
+        <v>1.73</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.4</v>
+        <v>1.03</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.3</v>
+        <v>1.45</v>
       </c>
       <c r="O12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P12" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T12" t="n">
         <v>3.25</v>
       </c>
-      <c r="P12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.97</v>
-      </c>
       <c r="U12" t="n">
-        <v>2.63</v>
+        <v>2.26</v>
       </c>
       <c r="V12" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z12" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AF12" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.48</v>
+        <v>2.43</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="O13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="P13" t="n">
-        <v>6.79</v>
+        <v>5.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="R13" t="n">
-        <v>2.46</v>
+        <v>2.75</v>
       </c>
       <c r="S13" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T13" t="n">
-        <v>3.34</v>
+        <v>4</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V13" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X13" t="n">
         <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.75</v>
+        <v>4.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AD13" t="n">
         <v>1.65</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,80 +2633,80 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>11</v>
+        <v>2.25</v>
       </c>
       <c r="O14" t="n">
-        <v>6.5</v>
+        <v>3.25</v>
       </c>
       <c r="P14" t="n">
-        <v>1.15</v>
+        <v>2.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>10.8</v>
+        <v>3.04</v>
       </c>
       <c r="R14" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T14" t="n">
         <v>3</v>
       </c>
-      <c r="S14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T14" t="n">
-        <v>4.3</v>
-      </c>
       <c r="U14" t="n">
-        <v>1.83</v>
+        <v>2.53</v>
       </c>
       <c r="V14" t="n">
-        <v>1.93</v>
+        <v>1.49</v>
       </c>
       <c r="W14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
         <v>1.27</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>4.85</v>
-      </c>
       <c r="AK14" t="n">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2804,19 +2804,19 @@
         <v>2.12</v>
       </c>
       <c r="R15" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S15" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T15" t="n">
-        <v>2.81</v>
+        <v>2.3</v>
       </c>
       <c r="U15" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="V15" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W15" t="n">
         <v>1.08</v>
@@ -2825,22 +2825,22 @@
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE15" t="n">
         <v>1.06</v>
@@ -2849,7 +2849,7 @@
         <v>1.91</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>4.9</v>
+        <v>3.55</v>
       </c>
       <c r="P16" t="n">
-        <v>5.74</v>
+        <v>1.57</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.75</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>2.53</v>
+        <v>2.25</v>
       </c>
       <c r="S16" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="T16" t="n">
-        <v>3.6</v>
+        <v>2.93</v>
       </c>
       <c r="U16" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="V16" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="W16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK16" t="n">
         <v>1.14</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>2.97</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="O17" t="n">
-        <v>3.95</v>
+        <v>3.84</v>
       </c>
       <c r="P17" t="n">
-        <v>4.97</v>
+        <v>5.72</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
         <v>1.3</v>
@@ -3134,40 +3134,40 @@
         <v>2.5</v>
       </c>
       <c r="V17" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W17" t="n">
         <v>1.11</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.9</v>
+        <v>3.78</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE17" t="n">
         <v>1.12</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AG17" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>1.17</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>5.05</v>
+        <v>1.3</v>
       </c>
       <c r="O18" t="n">
-        <v>3.55</v>
+        <v>4.65</v>
       </c>
       <c r="P18" t="n">
-        <v>1.56</v>
+        <v>8.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.5</v>
+        <v>1.75</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="S18" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T18" t="n">
-        <v>2.87</v>
+        <v>3.8</v>
       </c>
       <c r="U18" t="n">
-        <v>2.64</v>
+        <v>2.18</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.58</v>
+        <v>5.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.97</v>
+        <v>2.43</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.12</v>
+        <v>3.2</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3428,61 +3428,61 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="O19" t="n">
-        <v>3.23</v>
+        <v>3.38</v>
       </c>
       <c r="P19" t="n">
         <v>4.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="R19" t="n">
         <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U19" t="n">
         <v>3.33</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z19" t="n">
         <v>2.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AG19" t="n">
         <v>1.65</v>
@@ -3501,7 +3501,7 @@
         <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3587,80 +3587,80 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="O20" t="n">
         <v>3.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.81</v>
+        <v>3.45</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="R20" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="S20" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T20" t="n">
-        <v>3.17</v>
+        <v>2.96</v>
       </c>
       <c r="U20" t="n">
-        <v>2.71</v>
+        <v>2.53</v>
       </c>
       <c r="V20" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W20" t="n">
         <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z20" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AK20" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3749,25 +3749,25 @@
         <v>1.65</v>
       </c>
       <c r="O21" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="P21" t="n">
-        <v>4.21</v>
+        <v>3.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="R21" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S21" t="n">
         <v>1.29</v>
       </c>
       <c r="T21" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U21" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V21" t="n">
         <v>1.55</v>
@@ -3779,10 +3779,10 @@
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="AA21" t="n">
         <v>1.58</v>
@@ -3791,19 +3791,19 @@
         <v>2.19</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="AD21" t="n">
         <v>1.49</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>1.18</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="O22" t="n">
-        <v>3.35</v>
+        <v>3.48</v>
       </c>
       <c r="P22" t="n">
-        <v>3.23</v>
+        <v>3.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="R22" t="n">
         <v>2.28</v>
       </c>
       <c r="S22" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T22" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="U22" t="n">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="V22" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W22" t="n">
         <v>1.05</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
         <v>1.28</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF22" t="n">
         <v>1.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -725,16 +725,16 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="O2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P2" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="R2" t="n">
         <v>2.3</v>
@@ -746,10 +746,10 @@
         <v>2.88</v>
       </c>
       <c r="U2" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W2" t="n">
         <v>1.05</v>
@@ -770,10 +770,10 @@
         <v>1.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE2" t="n">
         <v>1.07</v>
@@ -782,7 +782,7 @@
         <v>2.2</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK2" t="n">
         <v>3.3</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4.9</v>
+        <v>1.85</v>
       </c>
       <c r="O3" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.72</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.1</v>
+        <v>2.7</v>
       </c>
       <c r="R3" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="S3" t="n">
         <v>1.55</v>
@@ -905,10 +905,10 @@
         <v>2.28</v>
       </c>
       <c r="U3" t="n">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W3" t="n">
         <v>1.02</v>
@@ -917,19 +917,19 @@
         <v>1.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AD3" t="n">
         <v>1.1</v>
@@ -938,10 +938,10 @@
         <v>1.02</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,80 +1043,80 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="O4" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="P4" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.51</v>
+        <v>2.28</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S4" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T4" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W4" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE4" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA4" t="n">
+      <c r="AF4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK4" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.83</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P5" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="R5" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="S5" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="T5" t="n">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="U5" t="n">
-        <v>3.58</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.41</v>
+        <v>2.88</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.1</v>
+        <v>3.84</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R6" t="n">
         <v>2.3</v>
       </c>
-      <c r="O6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.8</v>
-      </c>
       <c r="S6" t="n">
-        <v>1.59</v>
+        <v>1.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="U6" t="n">
-        <v>3.68</v>
+        <v>2.4</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.53</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.34</v>
+        <v>3.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.1</v>
+        <v>2.81</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.12</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.47</v>
+        <v>2.4</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,65 +1520,65 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.6</v>
+        <v>5.15</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>5.25</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.29</v>
+        <v>4.75</v>
       </c>
       <c r="R7" t="n">
         <v>1.95</v>
       </c>
       <c r="S7" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U7" t="n">
-        <v>3.32</v>
+        <v>3.7</v>
       </c>
       <c r="V7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="AA7" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF7" t="n">
         <v>2.25</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AG7" t="n">
         <v>1.57</v>
       </c>
-      <c r="AC7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.24</v>
+        <v>1.91</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.07</v>
+        <v>1.11</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.48</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P8" t="n">
-        <v>5.5</v>
+        <v>1.68</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.95</v>
+        <v>4.33</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U8" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="V8" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
         <v>1.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.81</v>
+        <v>2.43</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.4</v>
+        <v>1.17</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="O9" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="P9" t="n">
-        <v>1.68</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T9" t="n">
         <v>2.4</v>
       </c>
-      <c r="S9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.3</v>
-      </c>
       <c r="U9" t="n">
-        <v>2.48</v>
+        <v>3.68</v>
       </c>
       <c r="V9" t="n">
-        <v>1.51</v>
+        <v>1.2</v>
       </c>
       <c r="W9" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AF9" t="n">
-        <v>1.52</v>
+        <v>2.05</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>10.52</v>
+        <v>1.45</v>
       </c>
       <c r="O11" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="P11" t="n">
-        <v>1.14</v>
+        <v>5.85</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.789999999999999</v>
+        <v>1.91</v>
       </c>
       <c r="R11" t="n">
-        <v>3.28</v>
+        <v>2.5</v>
       </c>
       <c r="S11" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="T11" t="n">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="U11" t="n">
-        <v>1.87</v>
+        <v>2.26</v>
       </c>
       <c r="V11" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>7.3</v>
+        <v>4.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.47</v>
+        <v>1.18</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.73</v>
+        <v>2.07</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.03</v>
+        <v>2.43</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.45</v>
+        <v>2.25</v>
       </c>
       <c r="O12" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>5.85</v>
+        <v>2.6</v>
       </c>
       <c r="Q12" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB12" t="n">
         <v>1.91</v>
       </c>
-      <c r="R12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="AC12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
         <v>1.27</v>
       </c>
-      <c r="T12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AK12" t="n">
-        <v>2.43</v>
+        <v>1.41</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,65 +2474,65 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="O13" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="P13" t="n">
-        <v>5.75</v>
+        <v>4.8</v>
       </c>
       <c r="Q13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.83</v>
       </c>
-      <c r="R13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T13" t="n">
-        <v>4</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.88</v>
+        <v>2.15</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.25</v>
+        <v>1.38</v>
       </c>
       <c r="O14" t="n">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="P14" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB14" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AC14" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.19</v>
+        <v>2.04</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.41</v>
+        <v>2.88</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.57</v>
+        <v>10.52</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="P15" t="n">
-        <v>4.8</v>
+        <v>1.14</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.12</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2</v>
+        <v>3.28</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3</v>
+        <v>4.6</v>
       </c>
       <c r="U15" t="n">
-        <v>2.75</v>
+        <v>1.87</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.29</v>
+        <v>1.03</v>
       </c>
       <c r="Z15" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB15" t="n">
         <v>3.5</v>
       </c>
-      <c r="AA15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AC15" t="n">
-        <v>3.2</v>
+        <v>1.65</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.26</v>
+        <v>2.1</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.06</v>
+        <v>1.47</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.15</v>
+        <v>1.03</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="O16" t="n">
-        <v>3.55</v>
+        <v>4.65</v>
       </c>
       <c r="P16" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AA16" t="n">
         <v>1.57</v>
       </c>
-      <c r="Q16" t="n">
-        <v>5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AB16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF16" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC16" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AG16" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.14</v>
+        <v>3.2</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
-        <v>3.84</v>
+        <v>3.55</v>
       </c>
       <c r="P17" t="n">
-        <v>5.72</v>
+        <v>1.57</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T17" t="n">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="U17" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="V17" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="AB17" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.27</v>
+        <v>1.14</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="P18" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S18" t="n">
         <v>1.3</v>
       </c>
-      <c r="O18" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="P18" t="n">
-        <v>8.15</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.22</v>
-      </c>
       <c r="T18" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="U18" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="V18" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
         <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.2</v>
+        <v>3.78</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>1.17</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.2</v>
+        <v>2.27</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3431,19 +3431,19 @@
         <v>1.63</v>
       </c>
       <c r="O19" t="n">
-        <v>3.38</v>
+        <v>3.14</v>
       </c>
       <c r="P19" t="n">
         <v>4.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S19" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T19" t="n">
         <v>2.63</v>
@@ -3452,16 +3452,16 @@
         <v>3.33</v>
       </c>
       <c r="V19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W19" t="n">
         <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z19" t="n">
         <v>2.8</v>
@@ -3473,7 +3473,7 @@
         <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.82</v>
+        <v>3.68</v>
       </c>
       <c r="AD19" t="n">
         <v>1.2</v>
@@ -3482,10 +3482,10 @@
         <v>1.06</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK19" t="n">
         <v>2.05</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.85</v>
+        <v>5.15</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.7</v>
+        <v>4.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S3" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="U3" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="V3" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AE3" t="n">
         <v>1.02</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.16</v>
+        <v>1.91</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.8</v>
+        <v>1.11</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="O4" t="n">
-        <v>3.32</v>
+        <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="R4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB4" t="n">
         <v>2.05</v>
       </c>
-      <c r="S4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AC4" t="n">
-        <v>4.5</v>
+        <v>2.81</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,80 +1202,80 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="O5" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="P5" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.51</v>
+        <v>2.28</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S5" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T5" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W5" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA5" t="n">
+      <c r="AF5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK5" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.83</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.48</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>5.5</v>
+        <v>1.68</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.95</v>
+        <v>4.33</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T6" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U6" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="V6" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
         <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.81</v>
+        <v>2.43</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.4</v>
+        <v>1.17</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>5.15</v>
+        <v>1.85</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.75</v>
+        <v>2.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="T7" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="U7" t="n">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="V7" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W7" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AE7" t="n">
         <v>1.02</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.91</v>
+        <v>1.16</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>1.83</v>
       </c>
       <c r="O8" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P8" t="n">
-        <v>1.68</v>
+        <v>3.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.33</v>
+        <v>2.51</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="T8" t="n">
-        <v>3.3</v>
+        <v>2.47</v>
       </c>
       <c r="U8" t="n">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="W8" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z8" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.52</v>
+        <v>1.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.17</v>
+        <v>1.83</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.45</v>
+        <v>2.25</v>
       </c>
       <c r="O11" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>5.85</v>
+        <v>2.6</v>
       </c>
       <c r="Q11" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1.91</v>
       </c>
-      <c r="R11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="AC11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.27</v>
       </c>
-      <c r="T11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AK11" t="n">
-        <v>2.43</v>
+        <v>1.41</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,80 +2315,80 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.25</v>
+        <v>10.52</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="P12" t="n">
-        <v>2.6</v>
+        <v>1.14</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.04</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>2.11</v>
+        <v>3.28</v>
       </c>
       <c r="S12" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="U12" t="n">
-        <v>2.53</v>
+        <v>1.87</v>
       </c>
       <c r="V12" t="n">
-        <v>1.49</v>
+        <v>1.91</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y12" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AK12" t="n">
-        <v>1.41</v>
+        <v>1.03</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P13" t="n">
-        <v>4.8</v>
+        <v>5.85</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="U13" t="n">
-        <v>2.75</v>
+        <v>2.26</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.78</v>
+        <v>2.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.26</v>
+        <v>1.53</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.15</v>
+        <v>2.43</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,65 +2633,65 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="O14" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="P14" t="n">
-        <v>5.75</v>
+        <v>4.8</v>
       </c>
       <c r="Q14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.83</v>
       </c>
-      <c r="R14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T14" t="n">
-        <v>4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AH14" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.88</v>
+        <v>2.15</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>10.52</v>
+        <v>1.38</v>
       </c>
       <c r="O15" t="n">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="P15" t="n">
-        <v>1.14</v>
+        <v>5.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.789999999999999</v>
+        <v>1.83</v>
       </c>
       <c r="R15" t="n">
-        <v>3.28</v>
+        <v>2.75</v>
       </c>
       <c r="S15" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T15" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
       <c r="V15" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.3</v>
+        <v>4.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.65</v>
       </c>
-      <c r="AD15" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AE15" t="n">
-        <v>1.47</v>
+        <v>1.23</v>
       </c>
       <c r="AF15" t="n">
         <v>1.62</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.03</v>
+        <v>2.88</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="P16" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S16" t="n">
         <v>1.3</v>
       </c>
-      <c r="O16" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="P16" t="n">
-        <v>8.15</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.22</v>
-      </c>
       <c r="T16" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="U16" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="W16" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
         <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.2</v>
+        <v>3.78</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>1.17</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.2</v>
+        <v>2.27</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="O18" t="n">
-        <v>3.84</v>
+        <v>4.65</v>
       </c>
       <c r="P18" t="n">
-        <v>5.72</v>
+        <v>8.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T18" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="U18" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="V18" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
         <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.78</v>
+        <v>5.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AB18" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>1.17</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.27</v>
+        <v>3.2</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>5.15</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="R3" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="S3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AD3" t="n">
         <v>1.5</v>
       </c>
-      <c r="T3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AE3" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.91</v>
+        <v>1.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,80 +1043,80 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.48</v>
+        <v>1.83</v>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="P4" t="n">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.95</v>
+        <v>2.51</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
+      </c>
+      <c r="V4" t="n">
         <v>1.3</v>
       </c>
-      <c r="T4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.43</v>
-      </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
         <v>1.03</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AD4" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AE4" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AG4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK4" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>2.4</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="O5" t="n">
-        <v>3.32</v>
+        <v>2.7</v>
       </c>
       <c r="P5" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.28</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="S5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T5" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U5" t="n">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="V5" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="W5" t="n">
         <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>1.48</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="P6" t="n">
-        <v>1.68</v>
+        <v>5.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.33</v>
+        <v>1.95</v>
       </c>
       <c r="R6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.4</v>
       </c>
-      <c r="S6" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.48</v>
-      </c>
       <c r="V6" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
         <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.33</v>
+        <v>3.86</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.43</v>
+        <v>2.77</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.17</v>
+        <v>2.4</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.85</v>
+        <v>5.15</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.7</v>
+        <v>4.75</v>
       </c>
       <c r="R7" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S7" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="U7" t="n">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="V7" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AE7" t="n">
         <v>1.02</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.16</v>
+        <v>1.91</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.8</v>
+        <v>1.11</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O8" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="S8" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="T8" t="n">
-        <v>2.47</v>
+        <v>2.28</v>
       </c>
       <c r="U8" t="n">
-        <v>3</v>
+        <v>3.58</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.88</v>
+        <v>2.41</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.84</v>
+        <v>5.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="O9" t="n">
-        <v>2.7</v>
+        <v>3.32</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2.28</v>
       </c>
       <c r="R9" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="S9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T9" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U9" t="n">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.04</v>
+        <v>2.12</v>
       </c>
       <c r="R11" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="S11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="U11" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.91</v>
       </c>
-      <c r="AC11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AG11" t="n">
-        <v>2.19</v>
+        <v>1.83</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.41</v>
+        <v>2.15</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>10.52</v>
+        <v>1.38</v>
       </c>
       <c r="O12" t="n">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="P12" t="n">
-        <v>1.14</v>
+        <v>5.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.789999999999999</v>
+        <v>1.83</v>
       </c>
       <c r="R12" t="n">
-        <v>3.28</v>
+        <v>2.75</v>
       </c>
       <c r="S12" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T12" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="U12" t="n">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
       <c r="V12" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="W12" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.3</v>
+        <v>4.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.65</v>
       </c>
-      <c r="AD12" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AE12" t="n">
-        <v>1.47</v>
+        <v>1.23</v>
       </c>
       <c r="AF12" t="n">
         <v>1.62</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.03</v>
+        <v>2.88</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.45</v>
+        <v>10.52</v>
       </c>
       <c r="O13" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="P13" t="n">
-        <v>5.85</v>
+        <v>1.14</v>
       </c>
       <c r="Q13" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="R13" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V13" t="n">
         <v>1.91</v>
       </c>
-      <c r="R13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.53</v>
-      </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.4</v>
+        <v>7.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.07</v>
+        <v>1.73</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.43</v>
+        <v>1.03</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="O14" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P14" t="n">
-        <v>4.8</v>
+        <v>5.85</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>2.75</v>
+        <v>2.26</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.78</v>
+        <v>2.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.26</v>
+        <v>1.53</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.15</v>
+        <v>2.43</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,65 +2792,65 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.38</v>
+        <v>2.25</v>
       </c>
       <c r="O15" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>5.75</v>
+        <v>2.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.83</v>
+        <v>3.02</v>
       </c>
       <c r="R15" t="n">
-        <v>2.75</v>
+        <v>2.08</v>
       </c>
       <c r="S15" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>2.92</v>
       </c>
       <c r="U15" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="W15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.18</v>
       </c>
-      <c r="X15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.11</v>
-      </c>
       <c r="Z15" t="n">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="AC15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG15" t="n">
         <v>2.2</v>
       </c>
-      <c r="AD15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.88</v>
+        <v>1.42</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="O16" t="n">
-        <v>3.84</v>
+        <v>4.65</v>
       </c>
       <c r="P16" t="n">
-        <v>5.72</v>
+        <v>8.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="V16" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
         <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.78</v>
+        <v>5.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>1.17</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.27</v>
+        <v>3.2</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="P18" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S18" t="n">
         <v>1.3</v>
       </c>
-      <c r="O18" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="P18" t="n">
-        <v>8.15</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.22</v>
-      </c>
       <c r="T18" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="U18" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="V18" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
         <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.2</v>
+        <v>3.78</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>1.17</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.2</v>
+        <v>2.27</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -714,30 +714,30 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
         <v>1.37</v>
       </c>
       <c r="O2" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="P2" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="S2" t="n">
         <v>1.34</v>
@@ -746,10 +746,10 @@
         <v>2.88</v>
       </c>
       <c r="U2" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="V2" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W2" t="n">
         <v>1.05</v>
@@ -758,74 +758,74 @@
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF2" t="n">
         <v>2.2</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
+          <t>['57', '84', '86']</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ2" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.3</v>
+        <v>3.78</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46190.45833333334</v>
@@ -842,22 +842,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>5.15</v>
       </c>
       <c r="O3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U3" t="n">
         <v>3.75</v>
       </c>
-      <c r="P3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.47</v>
-      </c>
       <c r="V3" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE3" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AF3" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.2</v>
+        <v>1.91</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O4" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="P4" t="n">
-        <v>3.9</v>
+        <v>4.68</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="S4" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="T4" t="n">
-        <v>2.47</v>
+        <v>2.27</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X4" t="n">
         <v>1.06</v>
       </c>
-      <c r="X4" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y4" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.84</v>
+        <v>4.75</v>
       </c>
       <c r="AD4" t="n">
         <v>1.18</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,149 +1160,149 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R5" t="n">
         <v>2.3</v>
       </c>
-      <c r="O5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="S5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>['26', '81']</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
         <v>3</v>
       </c>
-      <c r="Q5" t="n">
-        <v>3</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-1</v>
-      </c>
       <c r="AN5" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46190.5</v>
@@ -1319,149 +1319,149 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>['43', '63']</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK6" t="n">
         <v>1.48</v>
       </c>
-      <c r="O6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="P6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AD6" t="n">
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AR6" t="n">
         <v>1.4</v>
       </c>
-      <c r="AE6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46190.5</v>
@@ -1478,32 +1478,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1512,115 +1512,115 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>5.15</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U7" t="n">
         <v>3</v>
       </c>
-      <c r="P7" t="n">
+      <c r="V7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q7" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AD7" t="n">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>['42']</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>['61', '90']</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AR7" t="n">
         <v>1.13</v>
       </c>
-      <c r="AE7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46190.5</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="R8" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="S8" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="T8" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="U8" t="n">
-        <v>3.58</v>
+        <v>3.15</v>
       </c>
       <c r="V8" t="n">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
         <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.41</v>
+        <v>2.74</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,149 +1796,149 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P9" t="n">
         <v>1.65</v>
       </c>
-      <c r="O9" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="P9" t="n">
-        <v>4.8</v>
-      </c>
       <c r="Q9" t="n">
-        <v>2.28</v>
+        <v>4.33</v>
       </c>
       <c r="R9" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="S9" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="T9" t="n">
-        <v>2.38</v>
+        <v>3.3</v>
       </c>
       <c r="U9" t="n">
-        <v>3.25</v>
+        <v>2.47</v>
       </c>
       <c r="V9" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.69</v>
+        <v>5</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.57</v>
+        <v>2.21</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.5</v>
+        <v>2.41</v>
       </c>
       <c r="AD9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>['30', '62']</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>['35']</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK9" t="n">
         <v>1.17</v>
       </c>
-      <c r="AE9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN9" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO9" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP9" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46190.5</v>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O10" t="n">
         <v>3.2</v>
@@ -2006,46 +2006,46 @@
         <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R10" t="n">
         <v>2.2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T10" t="n">
         <v>2.7</v>
       </c>
       <c r="U10" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="V10" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W10" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE10" t="n">
         <v>1.08</v>
@@ -2054,7 +2054,7 @@
         <v>1.7</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.57</v>
+        <v>2.35</v>
       </c>
       <c r="O11" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>4.8</v>
+        <v>2.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.12</v>
+        <v>3.02</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="S11" t="n">
         <v>1.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="U11" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
         <v>3.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.91</v>
+        <v>1.54</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.15</v>
+        <v>1.41</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="O12" t="n">
-        <v>4.6</v>
+        <v>4.15</v>
       </c>
       <c r="P12" t="n">
-        <v>5.75</v>
+        <v>5.85</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="R12" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="S12" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="T12" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="U12" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="V12" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="W12" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.9</v>
+        <v>4.45</v>
       </c>
       <c r="AA12" t="n">
         <v>1.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF12" t="n">
         <v>1.65</v>
       </c>
-      <c r="AE12" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AG12" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>10.52</v>
+        <v>11.42</v>
       </c>
       <c r="O13" t="n">
         <v>7</v>
@@ -2483,22 +2483,22 @@
         <v>1.14</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.789999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="R13" t="n">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="S13" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T13" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="U13" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="V13" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="W13" t="n">
         <v>1.25</v>
@@ -2507,13 +2507,13 @@
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AB13" t="n">
         <v>3.5</v>
@@ -2525,13 +2525,13 @@
         <v>2.1</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AK13" t="n">
         <v>1.03</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="O14" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P14" t="n">
-        <v>5.85</v>
+        <v>5.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="S14" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="T14" t="n">
-        <v>3.25</v>
+        <v>3.72</v>
       </c>
       <c r="U14" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="V14" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="W14" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.4</v>
+        <v>5.35</v>
       </c>
       <c r="AA14" t="n">
         <v>1.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.07</v>
+        <v>2.27</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.43</v>
+        <v>2.57</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.25</v>
+        <v>1.42</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.02</v>
+        <v>1.91</v>
       </c>
       <c r="R15" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="S15" t="n">
         <v>1.3</v>
       </c>
       <c r="T15" t="n">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="U15" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="V15" t="n">
         <v>1.44</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
         <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="AA15" t="n">
         <v>1.75</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.42</v>
+        <v>2.55</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="P16" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S16" t="n">
         <v>1.3</v>
       </c>
-      <c r="O16" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="P16" t="n">
-        <v>8.15</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.22</v>
-      </c>
       <c r="T16" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="U16" t="n">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="V16" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="W16" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
         <v>1.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.2</v>
+        <v>3.95</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.35</v>
+        <v>2.04</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.43</v>
+        <v>2.59</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>5</v>
+        <v>1.27</v>
       </c>
       <c r="O17" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="P17" t="n">
-        <v>1.57</v>
+        <v>6.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>1.68</v>
       </c>
       <c r="R17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AC17" t="n">
         <v>2.25</v>
       </c>
-      <c r="S17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.05</v>
-      </c>
       <c r="AD17" t="n">
-        <v>1.28</v>
+        <v>1.59</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.14</v>
+        <v>2.78</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.5</v>
+        <v>5.65</v>
       </c>
       <c r="O18" t="n">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="P18" t="n">
-        <v>5.72</v>
+        <v>1.46</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="R18" t="n">
         <v>2.3</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T18" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="U18" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="V18" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="W18" t="n">
         <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.17</v>
+        <v>1.98</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.27</v>
+        <v>1.13</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3431,25 +3431,25 @@
         <v>1.63</v>
       </c>
       <c r="O19" t="n">
-        <v>3.14</v>
+        <v>3.22</v>
       </c>
       <c r="P19" t="n">
         <v>4.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="R19" t="n">
         <v>2.1</v>
       </c>
       <c r="S19" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U19" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="V19" t="n">
         <v>1.3</v>
@@ -3458,19 +3458,19 @@
         <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
         <v>1.44</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AC19" t="n">
         <v>3.68</v>
@@ -3479,13 +3479,13 @@
         <v>1.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF19" t="n">
         <v>2.1</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3596,22 +3596,22 @@
         <v>3.45</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="R20" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="S20" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T20" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="U20" t="n">
         <v>2.53</v>
       </c>
       <c r="V20" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W20" t="n">
         <v>1.06</v>
@@ -3620,7 +3620,7 @@
         <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z20" t="n">
         <v>3.58</v>
@@ -3632,13 +3632,13 @@
         <v>1.95</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF20" t="n">
         <v>1.66</v>
@@ -3657,7 +3657,7 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK20" t="n">
         <v>1.91</v>
@@ -3749,55 +3749,55 @@
         <v>1.65</v>
       </c>
       <c r="O21" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="P21" t="n">
         <v>3.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S21" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T21" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U21" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V21" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W21" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AC21" t="n">
         <v>2.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF21" t="n">
         <v>1.57</v>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="O22" t="n">
-        <v>3.48</v>
+        <v>3.18</v>
       </c>
       <c r="P22" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="R22" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="S22" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T22" t="n">
         <v>3</v>
       </c>
       <c r="U22" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W22" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
         <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -852,16 +852,16 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -873,118 +873,118 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>5.15</v>
+        <v>1.85</v>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="P3" t="n">
-        <v>1.78</v>
+        <v>4.68</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.75</v>
+        <v>2.63</v>
       </c>
       <c r="R3" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="U3" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="V3" t="n">
         <v>1.25</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y3" t="n">
         <v>1.45</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.2</v>
+        <v>4.75</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
+          <t>['71', '90']</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ3" t="n">
-        <v>1.91</v>
+        <v>1.11</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46190.5</v>
@@ -1001,149 +1001,149 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.85</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="P4" t="n">
-        <v>4.68</v>
+        <v>1.65</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.63</v>
+        <v>4.33</v>
       </c>
       <c r="R4" t="n">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="S4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="V4" t="n">
         <v>1.52</v>
       </c>
-      <c r="T4" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.25</v>
-      </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.45</v>
+        <v>1.15</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.62</v>
+        <v>5</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.35</v>
+        <v>1.57</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.54</v>
+        <v>2.21</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.75</v>
+        <v>2.41</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30', '62']</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['35']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>1.11</v>
       </c>
-      <c r="AK4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46190.5</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,107 +1202,107 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>['43', '63']</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK5" t="n">
         <v>1.48</v>
       </c>
-      <c r="O5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="P5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>['26', '81']</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN5" t="n">
         <v>4</v>
       </c>
       <c r="AO5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AP5" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.49</v>
+        <v>1.89</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="AT5" t="n">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46190.5</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,107 +1361,107 @@
         </is>
       </c>
       <c r="N6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R6" t="n">
         <v>2.3</v>
       </c>
-      <c r="O6" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="S6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T6" t="n">
         <v>3.25</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="U6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>['26', '81']</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
         <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>['43', '63']</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>2</v>
       </c>
       <c r="AN6" t="n">
         <v>4</v>
       </c>
       <c r="AO6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AP6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.89</v>
+        <v>1.49</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AS6" t="n">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="AT6" t="n">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46190.5</v>
@@ -1647,139 +1647,139 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.57</v>
+        <v>5.15</v>
       </c>
       <c r="O8" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>5.25</v>
+        <v>1.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.25</v>
+        <v>4.75</v>
       </c>
       <c r="R8" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="S8" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="U8" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="V8" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="W8" t="n">
         <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.74</v>
+        <v>2.55</v>
       </c>
       <c r="AA8" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF8" t="n">
         <v>2.25</v>
       </c>
-      <c r="AB8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.17</v>
-      </c>
       <c r="AG8" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27', '32', '90+2']</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13', '22', '64', '86']</t>
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>1.91</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.2</v>
+        <v>1.11</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN8" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO8" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46190.5</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1821,13 +1821,13 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1838,107 +1838,107 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>1.57</v>
       </c>
       <c r="O9" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="P9" t="n">
-        <v>1.65</v>
+        <v>5.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.33</v>
+        <v>2.25</v>
       </c>
       <c r="R9" t="n">
-        <v>2.4</v>
+        <v>1.97</v>
       </c>
       <c r="S9" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="T9" t="n">
-        <v>3.3</v>
+        <v>2.44</v>
       </c>
       <c r="U9" t="n">
-        <v>2.47</v>
+        <v>3.15</v>
       </c>
       <c r="V9" t="n">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="W9" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>5</v>
+        <v>2.74</v>
       </c>
       <c r="AA9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.57</v>
       </c>
-      <c r="AB9" t="n">
-        <v>2.21</v>
-      </c>
       <c r="AC9" t="n">
-        <v>2.41</v>
+        <v>4.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.62</v>
+        <v>2.17</v>
       </c>
       <c r="AG9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>['49', '90+7']</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>['16']</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK9" t="n">
         <v>2.2</v>
       </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>['30', '62']</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>['35']</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AN9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AO9" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AP9" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.11</v>
+        <v>2.23</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.02</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS9" t="n">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="AT9" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46190.5</v>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1986,14 +1986,14 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2058,12 +2058,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['74']</t>
         </is>
       </c>
       <c r="AJ10" t="n">
@@ -2076,28 +2076,28 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN10" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO10" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP10" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46190.52083333334</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -2152,111 +2152,111 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.35</v>
+        <v>1.48</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="P11" t="n">
-        <v>2.62</v>
+        <v>5.85</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.02</v>
+        <v>1.91</v>
       </c>
       <c r="R11" t="n">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T11" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U11" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V11" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AF11" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
+          <t>['24']</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ11" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.41</v>
+        <v>2.4</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN11" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO11" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP11" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46190.54166666666</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,19 +2283,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -2307,72 +2307,72 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="O12" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P12" t="n">
-        <v>5.85</v>
+        <v>5.5</v>
       </c>
       <c r="Q12" t="n">
         <v>1.91</v>
       </c>
       <c r="R12" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S12" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="U12" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="V12" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W12" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.45</v>
+        <v>3.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.25</v>
+        <v>2.74</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2381,41 +2381,41 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO12" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP12" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU12" s="3" t="n">
         <v>46190.54166666666</v>
@@ -2442,139 +2442,139 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>11.42</v>
+        <v>1.43</v>
       </c>
       <c r="O13" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="P13" t="n">
-        <v>1.14</v>
+        <v>5.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.19</v>
+        <v>1.82</v>
       </c>
       <c r="R13" t="n">
-        <v>3.42</v>
+        <v>2.57</v>
       </c>
       <c r="S13" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T13" t="n">
-        <v>4.33</v>
+        <v>3.72</v>
       </c>
       <c r="U13" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="V13" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="W13" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.9</v>
+        <v>5.35</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.65</v>
+        <v>2.03</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.1</v>
+        <v>1.56</v>
       </c>
       <c r="AE13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>['23']</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>['28', '90+8']</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>1.44</v>
       </c>
-      <c r="AF13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU13" s="3" t="n">
         <v>46190.54166666666</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,22 +2601,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2625,115 +2625,115 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.43</v>
+        <v>2.35</v>
       </c>
       <c r="O14" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="P14" t="n">
-        <v>5.25</v>
+        <v>2.62</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.82</v>
+        <v>3.02</v>
       </c>
       <c r="R14" t="n">
-        <v>2.57</v>
+        <v>2.04</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T14" t="n">
-        <v>3.72</v>
+        <v>2.88</v>
       </c>
       <c r="U14" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="W14" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.35</v>
+        <v>3.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.03</v>
+        <v>2.88</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17', '38']</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['65']</t>
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.57</v>
+        <v>1.41</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN14" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO14" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP14" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU14" s="3" t="n">
         <v>46190.54166666666</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,139 +2760,139 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.42</v>
+        <v>11.42</v>
       </c>
       <c r="O15" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="P15" t="n">
-        <v>5.5</v>
+        <v>1.14</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.91</v>
+        <v>9.19</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3</v>
+        <v>3.42</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="T15" t="n">
-        <v>3.04</v>
+        <v>4.33</v>
       </c>
       <c r="U15" t="n">
-        <v>2.47</v>
+        <v>1.75</v>
       </c>
       <c r="V15" t="n">
+        <v>2</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.44</v>
       </c>
-      <c r="W15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X15" t="n">
+      <c r="AF15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>['62']</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>['15', '86']</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK15" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>2.55</v>
-      </c>
       <c r="AL15" t="n">
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN15" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO15" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP15" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AU15" s="3" t="n">
         <v>46190.54166666666</v>
@@ -2928,26 +2928,26 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['42', '60']</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22', '26', '53']</t>
         </is>
       </c>
       <c r="AJ16" t="n">
@@ -3030,28 +3030,28 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN16" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO16" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP16" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU16" s="3" t="n">
         <v>46190.58333333334</v>
@@ -3087,26 +3087,26 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1', '37', '41', '84']</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AJ17" t="n">
@@ -3189,28 +3189,28 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN17" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO17" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP17" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU17" s="3" t="n">
         <v>46190.58333333334</v>
@@ -3249,13 +3249,13 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AJ18" t="n">
@@ -3348,28 +3348,28 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO18" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AP18" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AU18" s="3" t="n">
         <v>46190.58333333334</v>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -1001,41 +1001,41 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" t="n">
         <v>2</v>
       </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1043,107 +1043,107 @@
         </is>
       </c>
       <c r="N4" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>['27', '32', '90+2']</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>['13', '22', '64', '86']</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN4" t="n">
         <v>4</v>
       </c>
-      <c r="O4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X4" t="n">
+      <c r="AO4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR4" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>['30', '62']</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>['35']</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AS4" t="n">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="AT4" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46190.5</v>
@@ -1170,31 +1170,31 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
         <v>2</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1202,107 +1202,107 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="O5" t="n">
-        <v>2.35</v>
+        <v>3.45</v>
       </c>
       <c r="P5" t="n">
-        <v>3.25</v>
+        <v>5.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="S5" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="T5" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="U5" t="n">
-        <v>3.74</v>
+        <v>3.15</v>
       </c>
       <c r="V5" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.4</v>
+        <v>2.74</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.95</v>
+        <v>4.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['49', '90+7']</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>['43', '63']</t>
+          <t>['16']</t>
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.48</v>
+        <v>2.2</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN5" t="n">
         <v>2</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>4</v>
       </c>
       <c r="AO5" t="n">
         <v>17</v>
       </c>
       <c r="AP5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.89</v>
+        <v>2.23</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.4</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS5" t="n">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AT5" t="n">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46190.5</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1329,31 +1329,31 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1361,107 +1361,107 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T6" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="W6" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AF6" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>['26', '81']</t>
+          <t>['61', '90']</t>
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AN6" t="n">
         <v>4</v>
       </c>
       <c r="AO6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.64</v>
+        <v>1.13</v>
       </c>
       <c r="AS6" t="n">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="AT6" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46190.5</v>
@@ -1478,149 +1478,149 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>['43', '63']</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
         <v>2</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>2</v>
-      </c>
-      <c r="O7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>['42']</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>['61', '90']</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>6</v>
       </c>
       <c r="AN7" t="n">
         <v>4</v>
       </c>
       <c r="AO7" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AP7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AT7" t="n">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46190.5</v>
@@ -1637,149 +1637,149 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
         <v>4</v>
       </c>
-      <c r="I8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>5.15</v>
-      </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="P8" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="R8" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="S8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.5</v>
       </c>
-      <c r="T8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>['27', '32', '90+2']</t>
+          <t>['30', '62']</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>['13', '22', '64', '86']</t>
+          <t>['35']</t>
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.91</v>
+        <v>1.2</v>
       </c>
       <c r="AK8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>1.11</v>
       </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="AS8" t="n">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="AT8" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46190.5</v>
@@ -1796,30 +1796,30 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>2</v>
       </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -1827,10 +1827,10 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1838,107 +1838,107 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="O9" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="P9" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="R9" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="S9" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.44</v>
+        <v>3.25</v>
       </c>
       <c r="U9" t="n">
-        <v>3.15</v>
+        <v>2.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.74</v>
+        <v>3.86</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.25</v>
+        <v>1.69</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.57</v>
+        <v>2.05</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.5</v>
+        <v>2.77</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.17</v>
+        <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.6</v>
+        <v>1.84</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>['49', '90+7']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>['16']</t>
+          <t>['26', '81']</t>
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AN9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AP9" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.23</v>
+        <v>1.49</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.64</v>
       </c>
       <c r="AS9" t="n">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="AT9" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46190.5</v>
@@ -2124,31 +2124,31 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2156,107 +2156,107 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.48</v>
+        <v>11.42</v>
       </c>
       <c r="O11" t="n">
-        <v>4.15</v>
+        <v>7</v>
       </c>
       <c r="P11" t="n">
-        <v>5.85</v>
+        <v>1.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.91</v>
+        <v>9.19</v>
       </c>
       <c r="R11" t="n">
-        <v>2.5</v>
+        <v>3.42</v>
       </c>
       <c r="S11" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="T11" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="U11" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.45</v>
+        <v>7.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>['24']</t>
+          <t>['62']</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15', '86']</t>
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.4</v>
+        <v>1.03</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AP11" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.26</v>
+        <v>2.13</v>
       </c>
       <c r="AS11" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="AT11" t="n">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46190.54166666666</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,22 +2283,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -2307,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2315,107 +2315,107 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="O12" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="P12" t="n">
-        <v>5.5</v>
+        <v>5.85</v>
       </c>
       <c r="Q12" t="n">
         <v>1.91</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T12" t="n">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="U12" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="V12" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.8</v>
+        <v>4.45</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.74</v>
+        <v>2.25</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
+          <t>['24']</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>['57']</t>
-        </is>
-      </c>
       <c r="AJ12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ12" t="n">
         <v>1.17</v>
       </c>
-      <c r="AK12" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0.57</v>
-      </c>
       <c r="AR12" t="n">
-        <v>0.88</v>
+        <v>1.26</v>
       </c>
       <c r="AS12" t="n">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="AT12" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="AU12" s="3" t="n">
         <v>46190.54166666666</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,22 +2601,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2633,107 +2633,107 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.35</v>
+        <v>1.42</v>
       </c>
       <c r="O14" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.62</v>
+        <v>5.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.02</v>
+        <v>1.91</v>
       </c>
       <c r="R14" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="S14" t="n">
         <v>1.3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="U14" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="V14" t="n">
         <v>1.44</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>['57']</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
         <v>2</v>
       </c>
-      <c r="AC14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>['17', '38']</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>['65']</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>5</v>
-      </c>
       <c r="AO14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AP14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.04</v>
+        <v>0.57</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.31</v>
+        <v>0.88</v>
       </c>
       <c r="AS14" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AT14" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="AU14" s="3" t="n">
         <v>46190.54166666666</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,28 +2760,28 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
         <v>2</v>
       </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>1</v>
@@ -2792,107 +2792,107 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>11.42</v>
+        <v>2.35</v>
       </c>
       <c r="O15" t="n">
-        <v>7</v>
+        <v>3.25</v>
       </c>
       <c r="P15" t="n">
-        <v>1.14</v>
+        <v>2.62</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.19</v>
+        <v>3.02</v>
       </c>
       <c r="R15" t="n">
-        <v>3.42</v>
+        <v>2.04</v>
       </c>
       <c r="S15" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="T15" t="n">
-        <v>4.33</v>
+        <v>2.88</v>
       </c>
       <c r="U15" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="V15" t="n">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="W15" t="n">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.9</v>
+        <v>3.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.28</v>
+        <v>1.73</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.65</v>
+        <v>2.88</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.1</v>
+        <v>1.37</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>['62']</t>
+          <t>['17', '38']</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>['15', '86']</t>
+          <t>['65']</t>
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN15" t="n">
         <v>5</v>
       </c>
       <c r="AO15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP15" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.13</v>
+        <v>1.31</v>
       </c>
       <c r="AS15" t="n">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="AT15" t="n">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="AU15" s="3" t="n">
         <v>46190.54166666666</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,25 +2919,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
         <v>3</v>
       </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -2951,107 +2951,107 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="O16" t="n">
-        <v>3.94</v>
+        <v>4.6</v>
       </c>
       <c r="P16" t="n">
-        <v>5.66</v>
+        <v>6.91</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="U16" t="n">
-        <v>2.44</v>
+        <v>2.16</v>
       </c>
       <c r="V16" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.04</v>
+        <v>2.62</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.59</v>
+        <v>2.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG16" t="n">
         <v>1.95</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>['42', '60']</t>
+          <t>['1', '37', '41', '84']</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>['22', '26', '53']</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.3</v>
+        <v>2.78</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AN16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AO16" t="n">
         <v>8</v>
       </c>
       <c r="AP16" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.19</v>
+        <v>1.64</v>
       </c>
       <c r="AS16" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="AT16" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AU16" s="3" t="n">
         <v>46190.58333333334</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,25 +3078,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
@@ -3110,107 +3110,107 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="O17" t="n">
-        <v>4.6</v>
+        <v>3.94</v>
       </c>
       <c r="P17" t="n">
-        <v>6.91</v>
+        <v>5.66</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T17" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="U17" t="n">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="V17" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="W17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.15</v>
       </c>
-      <c r="X17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Z17" t="n">
-        <v>5.5</v>
+        <v>3.95</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.62</v>
+        <v>2.04</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.25</v>
+        <v>2.59</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG17" t="n">
         <v>1.95</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>['1', '37', '41', '84']</t>
+          <t>['42', '60']</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>['22', '26', '53']</t>
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.78</v>
+        <v>2.3</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
       </c>
       <c r="AM17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN17" t="n">
         <v>4</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>7</v>
       </c>
       <c r="AO17" t="n">
         <v>8</v>
       </c>
       <c r="AP17" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.64</v>
+        <v>1.19</v>
       </c>
       <c r="AS17" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="AT17" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AU17" s="3" t="n">
         <v>46190.58333333334</v>
@@ -3405,26 +3405,26 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['29', '44', '74', '83']</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
@@ -3507,28 +3507,28 @@
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN19" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO19" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP19" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AU19" s="3" t="n">
         <v>46190.625</v>
@@ -3564,26 +3564,26 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+2']</t>
         </is>
       </c>
       <c r="AJ20" t="n">
@@ -3666,28 +3666,28 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN20" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO20" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP20" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU20" s="3" t="n">
         <v>46190.66666666666</v>
@@ -3742,23 +3742,23 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N21" t="n">
         <v>1.65</v>
       </c>
       <c r="O21" t="n">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="P21" t="n">
         <v>3.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="R21" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S21" t="n">
         <v>1.25</v>
@@ -3779,7 +3779,7 @@
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z21" t="n">
         <v>4.45</v>
@@ -3797,7 +3797,7 @@
         <v>1.48</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF21" t="n">
         <v>1.57</v>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK21" t="n">
         <v>2.1</v>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="O22" t="n">
         <v>3.18</v>
@@ -3956,13 +3956,13 @@
         <v>1.35</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF22" t="n">
         <v>1.71</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>

--- a/jogos_2026-06-17.xlsx
+++ b/jogos_2026-06-17.xlsx
@@ -852,31 +852,31 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
         <v>2</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -884,80 +884,80 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="P3" t="n">
-        <v>4.68</v>
+        <v>3.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="S3" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="T3" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="U3" t="n">
-        <v>3.3</v>
+        <v>3.74</v>
       </c>
       <c r="V3" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="Z3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA3" t="n">
         <v>2.62</v>
       </c>
-      <c r="AA3" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AB3" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.75</v>
+        <v>4.95</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>['71', '90']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['43', '63']</t>
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.87</v>
+        <v>1.48</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -966,25 +966,25 @@
         <v>2</v>
       </c>
       <c r="AN3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO3" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AP3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.06</v>
+        <v>1.89</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="AT3" t="n">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46190.5</v>
@@ -1001,38 +1001,38 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Rustavi</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -1043,107 +1043,107 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>5.15</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U4" t="n">
         <v>3</v>
       </c>
-      <c r="P4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3.75</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="W4" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X4" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.2</v>
+        <v>3.68</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>['27', '32', '90+2']</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>['13', '22', '64', '86']</t>
+          <t>['61', '90']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.91</v>
+        <v>1.32</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN4" t="n">
         <v>4</v>
       </c>
       <c r="AO4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AS4" t="n">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="AT4" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46190.5</v>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1185,13 +1185,13 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1202,107 +1202,107 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA5" t="n">
         <v>1.57</v>
       </c>
-      <c r="O5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="P5" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AB5" t="n">
-        <v>1.57</v>
+        <v>2.21</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.5</v>
+        <v>2.41</v>
       </c>
       <c r="AD5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>['30', '62']</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>['35']</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK5" t="n">
         <v>1.17</v>
       </c>
-      <c r="AE5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>['49', '90+7']</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>['16']</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO5" t="n">
         <v>9</v>
       </c>
-      <c r="AN5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>17</v>
-      </c>
       <c r="AP5" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.23</v>
+        <v>1.11</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.02</v>
       </c>
       <c r="AS5" t="n">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="AT5" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46190.5</v>
@@ -1319,149 +1319,149 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rustavi</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>2</v>
       </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
         <v>2</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
+      <c r="AG6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>['71', '90']</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
         <v>2</v>
       </c>
-      <c r="O6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W6" t="n">
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>1.06</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>['42']</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>['61', '90']</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AR6" t="n">
-        <v>1.13</v>
+        <v>0.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="AT6" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46190.5</v>
@@ -1488,31 +1488,31 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
         <v>2</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1520,107 +1520,107 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="O7" t="n">
-        <v>2.35</v>
+        <v>3.45</v>
       </c>
       <c r="P7" t="n">
-        <v>3.25</v>
+        <v>5.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="S7" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="T7" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="U7" t="n">
-        <v>3.74</v>
+        <v>3.15</v>
       </c>
       <c r="V7" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.4</v>
+        <v>2.74</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.95</v>
+        <v>4.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['49', '90+7']</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>['43', '63']</t>
+          <t>['16']</t>
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.48</v>
+        <v>2.2</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN7" t="n">
         <v>2</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>4</v>
       </c>
       <c r="AO7" t="n">
         <v>17</v>
       </c>
       <c r="AP7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.89</v>
+        <v>2.23</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.4</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS7" t="n">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AT7" t="n">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46190.5</v>
@@ -1647,31 +1647,31 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>2</v>
       </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1679,107 +1679,107 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>['26', '81']</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN8" t="n">
         <v>4</v>
       </c>
-      <c r="O8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>['30', '62']</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>['35']</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>5</v>
-      </c>
       <c r="AO8" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AP8" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.11</v>
+        <v>1.49</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.02</v>
+        <v>1.64</v>
       </c>
       <c r="AS8" t="n">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="AT8" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46190.5</v>
@@ -1796,41 +1796,41 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
         <v>2</v>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1838,107 +1838,107 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.48</v>
+        <v>5.15</v>
       </c>
       <c r="O9" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>5.5</v>
+        <v>1.78</v>
       </c>
       <c r="Q9" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R9" t="n">
         <v>1.95</v>
       </c>
-      <c r="R9" t="n">
-        <v>2.3</v>
-      </c>
       <c r="S9" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="T9" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="U9" t="n">
-        <v>2.4</v>
+        <v>3.75</v>
       </c>
       <c r="V9" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="W9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>['27', '32', '90+2']</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>['13', '22', '64', '86']</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AK9" t="n">
         <v>1.11</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>['26', '81']</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AN9" t="n">
         <v>4</v>
       </c>
       <c r="AO9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AP9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="AT9" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46190.5</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2139,13 +2139,13 @@
         <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
@@ -2156,107 +2156,107 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>11.42</v>
+        <v>1.43</v>
       </c>
       <c r="O11" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="P11" t="n">
-        <v>1.14</v>
+        <v>5.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.19</v>
+        <v>1.82</v>
       </c>
       <c r="R11" t="n">
-        <v>3.42</v>
+        <v>2.57</v>
       </c>
       <c r="S11" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T11" t="n">
-        <v>4.33</v>
+        <v>3.72</v>
       </c>
       <c r="U11" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="V11" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>7.9</v>
+        <v>5.35</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.65</v>
+        <v>2.03</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.1</v>
+        <v>1.56</v>
       </c>
       <c r="AE11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>['23']</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>['28', '90+8']</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>1.44</v>
       </c>
-      <c r="AF11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>['62']</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>['15', '86']</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AR11" t="n">
-        <v>2.13</v>
+        <v>1.63</v>
       </c>
       <c r="AS11" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="AT11" t="n">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46190.54166666666</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,22 +2283,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -2307,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2315,107 +2315,107 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.48</v>
+        <v>2.35</v>
       </c>
       <c r="O12" t="n">
-        <v>4.15</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>5.85</v>
+        <v>2.62</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.91</v>
+        <v>3.02</v>
       </c>
       <c r="R12" t="n">
-        <v>2.5</v>
+        <v>2.04</v>
       </c>
       <c r="S12" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U12" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V12" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W12" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.45</v>
+        <v>3.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AC12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG12" t="n">
         <v>2.25</v>
       </c>
-      <c r="AD12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>['24']</t>
+          <t>['17', '38']</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['65']</t>
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.4</v>
+        <v>1.41</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AS12" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="AT12" t="n">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="AU12" s="3" t="n">
         <v>46190.54166666666</v>
@@ -2442,31 +2442,31 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2474,107 +2474,107 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="O13" t="n">
-        <v>4.4</v>
+        <v>4.15</v>
       </c>
       <c r="P13" t="n">
-        <v>5.25</v>
+        <v>5.85</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="R13" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="T13" t="n">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="U13" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="V13" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="W13" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X13" t="n">
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.35</v>
+        <v>4.45</v>
       </c>
       <c r="AA13" t="n">
         <v>1.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>['23']</t>
+          <t>['24']</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>['28', '90+8']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
       <c r="AM13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN13" t="n">
         <v>4</v>
       </c>
-      <c r="AN13" t="n">
-        <v>6</v>
-      </c>
       <c r="AO13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP13" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.44</v>
+        <v>1.17</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.63</v>
+        <v>1.26</v>
       </c>
       <c r="AS13" t="n">
         <v>72</v>
       </c>
       <c r="AT13" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="AU13" s="3" t="n">
         <v>46190.54166666666</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,28 +2601,28 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>1</v>
@@ -2633,107 +2633,107 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.42</v>
+        <v>11.42</v>
       </c>
       <c r="O14" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="P14" t="n">
-        <v>5.5</v>
+        <v>1.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.91</v>
+        <v>9.19</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3</v>
+        <v>3.42</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="T14" t="n">
-        <v>3.04</v>
+        <v>4.33</v>
       </c>
       <c r="U14" t="n">
-        <v>2.47</v>
+        <v>1.75</v>
       </c>
       <c r="V14" t="n">
+        <v>2</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.44</v>
       </c>
-      <c r="W14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X14" t="n">
+      <c r="AF14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>['62']</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>['15', '86']</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK14" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>['57']</t>
-        </is>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>2.55</v>
-      </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AO14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AP14" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.57</v>
+        <v>1.15</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.88</v>
+        <v>2.13</v>
       </c>
       <c r="AS14" t="n">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="AT14" t="n">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="AU14" s="3" t="n">
         <v>46190.54166666666</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,22 +2760,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2792,107 +2792,107 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.35</v>
+        <v>1.42</v>
       </c>
       <c r="O15" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.62</v>
+        <v>5.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.02</v>
+        <v>1.91</v>
       </c>
       <c r="R15" t="n">
-        <v>2.04</v>
+        <v>2.3</v>
       </c>
       <c r="S15" t="n">
         <v>1.3</v>
       </c>
       <c r="T15" t="n">
-        <v>2.88</v>
+        <v>3.04</v>
       </c>
       <c r="U15" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="V15" t="n">
         <v>1.44</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>['57']</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
         <v>2</v>
       </c>
-      <c r="AC15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>['17', '38']</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>['65']</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>5</v>
-      </c>
       <c r="AO15" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AP15" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.04</v>
+        <v>0.57</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.31</v>
+        <v>0.88</v>
       </c>
       <c r="AS15" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AT15" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="AU15" s="3" t="n">
         <v>46190.54166666666</v>
@@ -2919,139 +2919,139 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z16" t="n">
         <v>4</v>
       </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="O16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P16" t="n">
-        <v>6.91</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AA16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.44</v>
       </c>
-      <c r="AB16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AE16" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>['1', '37', '41', '84']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.17</v>
+        <v>1.98</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.78</v>
+        <v>1.13</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO16" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AP16" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.08</v>
+        <v>0.44</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AS16" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="AT16" t="n">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="AU16" s="3" t="n">
         <v>46190.58333333334</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,25 +3078,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
         <v>3</v>
       </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
@@ -3110,107 +3110,107 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="O17" t="n">
-        <v>3.94</v>
+        <v>4.6</v>
       </c>
       <c r="P17" t="n">
-        <v>5.66</v>
+        <v>6.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T17" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="U17" t="n">
-        <v>2.44</v>
+        <v>2.16</v>
       </c>
       <c r="V17" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.04</v>
+        <v>2.62</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.59</v>
+        <v>2.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG17" t="n">
         <v>1.95</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>['42', '60']</t>
+          <t>['1', '37', '41', '84']</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>['22', '26', '53']</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.3</v>
+        <v>2.78</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AN17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AO17" t="n">
         <v>8</v>
       </c>
       <c r="AP17" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.19</v>
+        <v>1.64</v>
       </c>
       <c r="AS17" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="AT17" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AU17" s="3" t="n">
         <v>46190.58333333334</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,31 +3237,31 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -3269,107 +3269,107 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>5.65</v>
+        <v>1.5</v>
       </c>
       <c r="O18" t="n">
-        <v>3.85</v>
+        <v>3.94</v>
       </c>
       <c r="P18" t="n">
-        <v>1.46</v>
+        <v>5.66</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
         <v>2.3</v>
       </c>
       <c r="S18" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T18" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="U18" t="n">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="V18" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W18" t="n">
         <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>['42', '60']</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>['22', '26', '53']</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN18" t="n">
         <v>4</v>
       </c>
-      <c r="AA18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>['39']</t>
-        </is>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>6</v>
-      </c>
       <c r="AO18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AP18" t="n">
         <v>9</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.44</v>
+        <v>1.05</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="AS18" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="AT18" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="AU18" s="3" t="n">
         <v>46190.58333333334</v>
